--- a/datos/maestros/md_jugadores.xlsx
+++ b/datos/maestros/md_jugadores.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E798"/>
+  <dimension ref="A1:E799"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21974,6 +21974,33 @@
         </is>
       </c>
     </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>6aa6ba47ae69100406100094</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>Burcio</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>504e581e4d8bec9a670000d9</t>
+        </is>
+      </c>
+      <c r="D799" t="inlineStr">
+        <is>
+          <t>centrocampista</t>
+        </is>
+      </c>
+      <c r="E799" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/maestros/md_jugadores.xlsx
+++ b/datos/maestros/md_jugadores.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E799"/>
+  <dimension ref="A1:E800"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22001,6 +22001,33 @@
         </is>
       </c>
     </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>6aa9ba57968b3203e1b9f655</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>Mayol</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>504e581e4d8bec9a670000cb</t>
+        </is>
+      </c>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>centrocampista</t>
+        </is>
+      </c>
+      <c r="E800" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/maestros/md_jugadores.xlsx
+++ b/datos/maestros/md_jugadores.xlsx
@@ -7991,22 +7991,22 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>5767a067e854a6271e7ff173</t>
+          <t>6a35ba801636ff03e132961e</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Toni Martínez</t>
+          <t>Gijselhart</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -8018,17 +8018,17 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>5634f6a0268e529b04ff8c45</t>
+          <t>5767a067e854a6271e7ff173</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Borja Mayoral</t>
+          <t>Toni Martínez</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -8045,22 +8045,22 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>52079128fa700fba29000016</t>
+          <t>5634f6a0268e529b04ff8c45</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Pere Milla</t>
+          <t>Borja Mayoral</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -8072,22 +8072,22 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>5591624ea1736b3a42844561</t>
+          <t>52079128fa700fba29000016</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Villalibre</t>
+          <t>Pere Milla</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -8099,22 +8099,22 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>52017ff1cf55e01b3400002e</t>
+          <t>5591624ea1736b3a42844561</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Mandi</t>
+          <t>Villalibre</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -8126,17 +8126,17 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>57363a66ad212396073bce9f</t>
+          <t>52017ff1cf55e01b3400002e</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Zubeldia</t>
+          <t>Mandi</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -8153,22 +8153,22 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>5201061f19cbe478070000c6</t>
+          <t>57363a66ad212396073bce9f</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Sergio Herrera</t>
+          <t>Zubeldia</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -8180,17 +8180,17 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>5202890bd7a595bd3700007b</t>
+          <t>5201061f19cbe478070000c6</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t xml:space="preserve">Germán </t>
+          <t>Sergio Herrera</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -8207,17 +8207,17 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>5214d165dbf8b74f020000e3</t>
+          <t>5202890bd7a595bd3700007b</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Aitor Fernández</t>
+          <t xml:space="preserve">Germán </t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -8234,12 +8234,12 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>574dc94bb9278bf5518b1e7b</t>
+          <t>5214d165dbf8b74f020000e3</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Budimir</t>
+          <t>Aitor Fernández</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -8249,7 +8249,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -8261,22 +8261,22 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>5402cba8e8a4c9292a000287</t>
+          <t>574dc94bb9278bf5518b1e7b</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Christensen</t>
+          <t>Budimir</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -8288,17 +8288,17 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>50d2514b099731b00e02ee94</t>
+          <t>5402cba8e8a4c9292a000287</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Laporte</t>
+          <t>Christensen</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -8315,17 +8315,17 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>51b89bd5e401a15f2c000140</t>
+          <t>50d2514b099731b00e02ee94</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Cabrera</t>
+          <t>Laporte</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -8342,17 +8342,17 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>504f65024d8bec9a670005a6</t>
+          <t>51b89bd5e401a15f2c000140</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Ximo Navarro</t>
+          <t>Cabrera</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -8369,12 +8369,12 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>523473325a4ad28f01000014</t>
+          <t>504f65024d8bec9a670005a6</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Giménez</t>
+          <t>Ximo Navarro</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -8396,22 +8396,22 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>55b66bc6fe0ded1c22ebbd6d</t>
+          <t>523473325a4ad28f01000014</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Dmitrovic</t>
+          <t>Giménez</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -8423,22 +8423,22 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>520d1ce5a776cc826b000026</t>
+          <t>55b66bc6fe0ded1c22ebbd6d</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Lucas Torró</t>
+          <t>Dmitrovic</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -8450,22 +8450,22 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>525d4f895231f4d645000795</t>
+          <t>520d1ce5a776cc826b000026</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Iván Villar</t>
+          <t>Lucas Torró</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -8477,22 +8477,22 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>5442eeb84e1f41e97e000261</t>
+          <t>525d4f895231f4d645000795</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Bellerin</t>
+          <t>Iván Villar</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -8504,17 +8504,17 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>544dfb9b322ce8ed010002bf</t>
+          <t>5442eeb84e1f41e97e000261</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Djené</t>
+          <t>Bellerin</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -8531,22 +8531,22 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>56787538d0e498cf3e24cda6</t>
+          <t>544dfb9b322ce8ed010002bf</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Guruzeta</t>
+          <t>Djené</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -8558,22 +8558,22 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>522f8e353ce1ab673f00000b</t>
+          <t>56787538d0e498cf3e24cda6</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Bartra</t>
+          <t>Guruzeta</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -8585,22 +8585,22 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>522ccdebe10a44087f0000ec</t>
+          <t>522f8e353ce1ab673f00000b</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Unai López</t>
+          <t>Bartra</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -8612,17 +8612,17 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>504e58594d8bec9a67000106</t>
+          <t>522ccdebe10a44087f0000ec</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Galarreta</t>
+          <t>Unai López</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -8639,22 +8639,22 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>520d0d314386b4816b000029</t>
+          <t>504e58594d8bec9a67000106</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Alfonso Herrero</t>
+          <t>Galarreta</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -8666,22 +8666,22 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>51b895eae401a15f2c00012d</t>
+          <t>520d0d314386b4816b000029</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Moi Gómez</t>
+          <t>Alfonso Herrero</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -8693,17 +8693,17 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>504e58bb4d8bec9a67000187</t>
+          <t>51b895eae401a15f2c00012d</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Koke</t>
+          <t>Moi Gómez</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -8720,22 +8720,22 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>53df365ce5c94c6a08000203</t>
+          <t>504e58bb4d8bec9a67000187</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Kiko Femenía</t>
+          <t>Koke</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -8747,22 +8747,22 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>520243d0d7a595bd3700001f</t>
+          <t>53df365ce5c94c6a08000203</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Oblak</t>
+          <t>Kiko Femenía</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -8774,22 +8774,22 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>5676df0e008eb5c93e62f205</t>
+          <t>520243d0d7a595bd3700001f</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Sadiq Umar</t>
+          <t>Oblak</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -8801,12 +8801,12 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>520d201ca776cc826b000029</t>
+          <t>5676df0e008eb5c93e62f205</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Luis Rioja</t>
+          <t>Sadiq Umar</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -8816,7 +8816,7 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -8828,22 +8828,22 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>521a999b5865e5687000001c</t>
+          <t>520d201ca776cc826b000029</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t xml:space="preserve">David Soria </t>
+          <t>Luis Rioja</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
@@ -8855,22 +8855,22 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>5738fcf88179bfa8526e19ce</t>
+          <t>521a999b5865e5687000001c</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Sergi Canós</t>
+          <t xml:space="preserve">David Soria </t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -8882,22 +8882,22 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>51b9e593e401a15f2c00019f</t>
+          <t>5738fcf88179bfa8526e19ce</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Toljan</t>
+          <t>Sergi Canós</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -8909,22 +8909,22 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>51d71d02a7178a7654000017</t>
+          <t>51b9e593e401a15f2c00019f</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Aubameyang</t>
+          <t>Toljan</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -8936,22 +8936,22 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>5203972e2e80d2950b00016f</t>
+          <t>51d71d02a7178a7654000017</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>J. Musso</t>
+          <t>Aubameyang</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
@@ -8963,22 +8963,22 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>520d29408091fd886b000049</t>
+          <t>5203972e2e80d2950b00016f</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Mariano</t>
+          <t>J. Musso</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -8990,22 +8990,22 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>5590e248b804493642903cdc</t>
+          <t>520d29408091fd886b000049</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Remiro</t>
+          <t>Mariano</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -9017,22 +9017,22 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>53c61e5c3554a2ca66000014</t>
+          <t>5590e248b804493642903cdc</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Lejeune</t>
+          <t>Remiro</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -9044,22 +9044,22 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>52175e9470a79164260001a4</t>
+          <t>53c61e5c3554a2ca66000014</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Borja Iglesias</t>
+          <t>Lejeune</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -9071,22 +9071,22 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>5590e613b804493642903d44</t>
+          <t>52175e9470a79164260001a4</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Yeray</t>
+          <t>Borja Iglesias</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -9098,22 +9098,22 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>504f50c54d8bec9a670003d1</t>
+          <t>5590e613b804493642903d44</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Iago Aspas</t>
+          <t>Yeray</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -9125,22 +9125,22 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>505d8a247e438909310001c5</t>
+          <t>504f50c54d8bec9a670003d1</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Rubén García</t>
+          <t>Iago Aspas</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -9152,22 +9152,22 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>53df321ae5c94c6a08000200</t>
+          <t>505d8a247e438909310001c5</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Marcos Llorente</t>
+          <t>Rubén García</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -9179,22 +9179,22 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>521464ea0c36b84d02000024</t>
+          <t>53df321ae5c94c6a08000200</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Raúl de Tomás</t>
+          <t>Marcos Llorente</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -9206,22 +9206,22 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>52017ff55430e20e34000036</t>
+          <t>521464ea0c36b84d02000024</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Foulquier</t>
+          <t>Raúl de Tomás</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -9233,12 +9233,12 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>5218979184abda6d26000258</t>
+          <t>52017ff55430e20e34000036</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Dimitrievski</t>
+          <t>Foulquier</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -9248,7 +9248,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -9260,22 +9260,22 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>50f47dd1dbbab36d0e0042e3</t>
+          <t>5218979184abda6d26000258</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Jonny</t>
+          <t>Dimitrievski</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -9287,17 +9287,17 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>5255d8008e3e4c1352000369</t>
+          <t>50f47dd1dbbab36d0e0042e3</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Odriozola</t>
+          <t>Jonny</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -9314,22 +9314,22 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>56ff01f1f4bbe2a5799eb126</t>
+          <t>5255d8008e3e4c1352000369</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Kike García</t>
+          <t>Odriozola</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -9341,22 +9341,22 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>54b25febc9360f7e58002e7c</t>
+          <t>56ff01f1f4bbe2a5799eb126</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Berenguer</t>
+          <t>Kike García</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -9368,22 +9368,22 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>504f50d44d8bec9a6700040e</t>
+          <t>54b25febc9360f7e58002e7c</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Ayoze Pérez</t>
+          <t>Berenguer</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -9395,22 +9395,22 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>55916197c498293442727262</t>
+          <t>504f50d44d8bec9a6700040e</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Unai Simón</t>
+          <t>Ayoze Pérez</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
@@ -9422,22 +9422,22 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>52013ee178b20d7f07000351</t>
+          <t>55916197c498293442727262</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Josan</t>
+          <t>Unai Simón</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
@@ -9449,22 +9449,22 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>575c2bacaf91c7b04d8c2513</t>
+          <t>52013ee178b20d7f07000351</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Boyé</t>
+          <t>Josan</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -9476,22 +9476,22 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>535d291c74bf632c030004d2</t>
+          <t>575c2bacaf91c7b04d8c2513</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Gayá</t>
+          <t>Boyé</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -9503,22 +9503,22 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>504f65184d8bec9a670005f7</t>
+          <t>535d291c74bf632c030004d2</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Isco</t>
+          <t>Gayá</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
@@ -9530,22 +9530,22 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>5659df7ca6379cbb070b8d84</t>
+          <t>504f65184d8bec9a670005f7</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Oyarzabal</t>
+          <t>Isco</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
@@ -9557,22 +9557,22 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>5218a3a884abda6d26000265</t>
+          <t>5659df7ca6379cbb070b8d84</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Álvaro García</t>
+          <t>Oyarzabal</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
@@ -9584,17 +9584,17 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>53a01453b33bed3b010002b1</t>
+          <t>5218a3a884abda6d26000265</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Denis Suárez</t>
+          <t>Álvaro García</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -9611,22 +9611,22 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>504f65024d8bec9a670005aa</t>
+          <t>53a01453b33bed3b010002b1</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Bigas</t>
+          <t>Denis Suárez</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
@@ -9638,22 +9638,22 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>57c09dd1f40c42594caa2956</t>
+          <t>504f65024d8bec9a670005aa</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Marc Roca</t>
+          <t>Bigas</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
@@ -9665,22 +9665,22 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>51c1ca53c7694f5f66000015</t>
+          <t>57c09dd1f40c42594caa2956</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Rüdiger</t>
+          <t>Marc Roca</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
@@ -9692,17 +9692,17 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>51bcc43bb9eca82e1a000011</t>
+          <t>51c1ca53c7694f5f66000015</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Marcos Alonso</t>
+          <t>Rüdiger</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -9719,22 +9719,22 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>51b897a5e401a15f2c000139</t>
+          <t>51bcc43bb9eca82e1a000011</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Gerard Moreno</t>
+          <t>Marcos Alonso</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
@@ -9746,22 +9746,22 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>5606c6f48ec803b3053e1b04</t>
+          <t>51b897a5e401a15f2c000139</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Fornals</t>
+          <t>Gerard Moreno</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
@@ -9773,12 +9773,12 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>51aa7cb4a56ca45802050abe</t>
+          <t>5606c6f48ec803b3053e1b04</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Diego Llorente</t>
+          <t>Fornals</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -9788,7 +9788,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -9800,22 +9800,22 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>548336cc78a053bf06000ce5</t>
+          <t>51aa7cb4a56ca45802050abe</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Iñaki Williams</t>
+          <t>Diego Llorente</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
@@ -9827,22 +9827,22 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>598b2b3e96ef719d4b46b147</t>
+          <t>548336cc78a053bf06000ce5</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Barja</t>
+          <t>Iñaki Williams</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
@@ -9854,17 +9854,17 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>5962a95af5056e652d290af9</t>
+          <t>598b2b3e96ef719d4b46b147</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Tete Morente</t>
+          <t>Barja</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -9881,22 +9881,22 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>592c5d96e0882ebf0514d517</t>
+          <t>5962a95af5056e652d290af9</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Gabriel Suazo</t>
+          <t>Tete Morente</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -9908,22 +9908,22 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>57e816de3c438763749abb90</t>
+          <t>592c5d96e0882ebf0514d517</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Álvaro Fernández</t>
+          <t>Gabriel Suazo</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
@@ -9935,22 +9935,22 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>5b33dff53200b74d1d72171e</t>
+          <t>57e816de3c438763749abb90</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Catena</t>
+          <t>Álvaro Fernández</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
@@ -9962,17 +9962,17 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>5b35434b6268503b1d665ec1</t>
+          <t>5b33dff53200b74d1d72171e</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Diakhaby</t>
+          <t>Catena</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -9989,12 +9989,12 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>5a00fee9772e5c4f5827fbeb</t>
+          <t>5b35434b6268503b1d665ec1</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Guido Rodríguez</t>
+          <t>Diakhaby</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -10004,7 +10004,7 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
@@ -10016,22 +10016,22 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>5d51a911d191dc3feef552c0</t>
+          <t>5a00fee9772e5c4f5827fbeb</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Balliu</t>
+          <t>Guido Rodríguez</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
@@ -10043,22 +10043,22 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>5b89b1161c0c9f16f9678cba</t>
+          <t>5d51a911d191dc3feef552c0</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Lo Celso</t>
+          <t>Balliu</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
@@ -10070,17 +10070,17 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>5d6d88ad1ad6ea0475d2ea30</t>
+          <t>5b89b1161c0c9f16f9678cba</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Ciss</t>
+          <t>Lo Celso</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -10097,17 +10097,17 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>5d01a0892111645ef81548f8</t>
+          <t>5d6d88ad1ad6ea0475d2ea30</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>De Jong</t>
+          <t>Ciss</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -10124,22 +10124,22 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>60b40cb9d2d7f04662cc9c19</t>
+          <t>5d01a0892111645ef81548f8</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Omar</t>
+          <t>De Jong</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
@@ -10151,22 +10151,22 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>5d4bf0557474677ad684915a</t>
+          <t>60b40cb9d2d7f04662cc9c19</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Pedri</t>
+          <t>Omar</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
@@ -10178,22 +10178,22 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>60d6578de348bc03e95ba4b2</t>
+          <t>5d4bf0557474677ad684915a</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Copete</t>
+          <t>Pedri</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
@@ -10205,22 +10205,22 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>612183f216ab17088eaf36b1</t>
+          <t>60d6578de348bc03e95ba4b2</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Satriano</t>
+          <t>Copete</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
@@ -10232,22 +10232,22 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>5d5ea4ec12a917530bc3e4b0</t>
+          <t>612183f216ab17088eaf36b1</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Kubo</t>
+          <t>Satriano</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
@@ -10259,22 +10259,22 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>5d8a75210298d1049e864191</t>
+          <t>5d5ea4ec12a917530bc3e4b0</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Raúl</t>
+          <t>Kubo</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
@@ -10286,22 +10286,22 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>61d98435c40342041fe941b4</t>
+          <t>5d8a75210298d1049e864191</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Leo Román</t>
+          <t>Raúl</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
@@ -10313,22 +10313,22 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>5f45502cae94c503ccbd573f</t>
+          <t>61d98435c40342041fe941b4</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Fidalgo</t>
+          <t>Leo Román</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
@@ -10340,17 +10340,17 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>62d034b9fbbaa82d7199978b</t>
+          <t>5f45502cae94c503ccbd573f</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Beñat Prados</t>
+          <t>Fidalgo</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -10367,22 +10367,22 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>5f6b104d6a93e44a2fcc725e</t>
+          <t>62d034b9fbbaa82d7199978b</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Cristian Rivero</t>
+          <t>Beñat Prados</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
@@ -10394,22 +10394,22 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>6494b8e92ba0ab1e468b7f35</t>
+          <t>5f6b104d6a93e44a2fcc725e</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Bellingham</t>
+          <t>Cristian Rivero</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
@@ -10421,17 +10421,17 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>64c039a313c6a63ccc321929</t>
+          <t>6494b8e92ba0ab1e468b7f35</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Luismi Cruz</t>
+          <t>Bellingham</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
@@ -10448,22 +10448,22 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>5fecc9d86ede9207a9f2fcac</t>
+          <t>64c039a313c6a63ccc321929</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Juan Iglesias</t>
+          <t>Luismi Cruz</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
@@ -10475,22 +10475,22 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>64e53d084068dc518b94a054</t>
+          <t>5fecc9d86ede9207a9f2fcac</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Zakharyan</t>
+          <t>Juan Iglesias</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
@@ -10502,17 +10502,17 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>6080ace3876c8206f41c4197</t>
+          <t>64e53d084068dc518b94a054</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Blanco</t>
+          <t>Zakharyan</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
@@ -10529,22 +10529,22 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>66802f240c14414136e408c3</t>
+          <t>6080ace3876c8206f41c4197</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Mella</t>
+          <t>Blanco</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
@@ -10556,22 +10556,22 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>6110e7e0c16ee36065aa49bd</t>
+          <t>66802f240c14414136e408c3</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Agirrezabala</t>
+          <t>Mella</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
@@ -10583,17 +10583,17 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>6685186cd766964157307273</t>
+          <t>6110e7e0c16ee36065aa49bd</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Vlachodimos</t>
+          <t>Agirrezabala</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
@@ -10610,22 +10610,22 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>62a67388de8e9e03e103990b</t>
+          <t>6685186cd766964157307273</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Tchouameni</t>
+          <t>Vlachodimos</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
@@ -10637,22 +10637,22 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>6692e7f199e2e504052cb421</t>
+          <t>62a67388de8e9e03e103990b</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Letacek</t>
+          <t>Tchouameni</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
@@ -10664,22 +10664,22 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>62c81fc9deea5c2d8c81fe13</t>
+          <t>6692e7f199e2e504052cb421</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Peque</t>
+          <t>Letacek</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
@@ -10691,22 +10691,22 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>6861a4f450c8fc331b6365a2</t>
+          <t>62c81fc9deea5c2d8c81fe13</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Gerenabarrena</t>
+          <t>Peque</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
@@ -10718,22 +10718,22 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>64b8620a5595c73cc509b299</t>
+          <t>6861a4f450c8fc331b6365a2</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Alemão</t>
+          <t>Gerenabarrena</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
@@ -10745,22 +10745,22 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>68a3a86d3a1cb503e4687030</t>
+          <t>64b8620a5595c73cc509b299</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Martim Neto</t>
+          <t>Alemão</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
@@ -10772,22 +10772,22 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>64d156d341f8d73d235026fb</t>
+          <t>68a3a86d3a1cb503e4687030</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Natan</t>
+          <t>Martim Neto</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
@@ -10799,22 +10799,22 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>6961830c619f3203bc795c50</t>
+          <t>64d156d341f8d73d235026fb</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Joselu</t>
+          <t>Natan</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
@@ -10826,22 +10826,22 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>64e53d94a577ee5151c0b1f4</t>
+          <t>6961830c619f3203bc795c50</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Unai Marrero</t>
+          <t>Joselu</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
@@ -10853,22 +10853,22 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>6599dd40a4082870148ee34a</t>
+          <t>64e53d94a577ee5151c0b1f4</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Huijsen</t>
+          <t>Unai Marrero</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
@@ -10880,17 +10880,17 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>65aac8411342fe045bb822e2</t>
+          <t>6599dd40a4082870148ee34a</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Tárrega</t>
+          <t>Huijsen</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
@@ -10907,17 +10907,17 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>6a4d1bfcae633549bd0f0744</t>
+          <t>65aac8411342fe045bb822e2</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Bright Ede</t>
+          <t>Tárrega</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
@@ -10934,22 +10934,22 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>6653899c36df000455d63bf7</t>
+          <t>6a4d1bfcae633549bd0f0744</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Espí</t>
+          <t>Bright Ede</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
@@ -10961,22 +10961,22 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>66b78ac399e2e504052cbe93</t>
+          <t>6653899c36df000455d63bf7</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Marc Bernal</t>
+          <t>Espí</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
@@ -10988,22 +10988,22 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>66cfa0f08be9a7041ad309f9</t>
+          <t>66b78ac399e2e504052cbe93</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Jon Martín</t>
+          <t>Marc Bernal</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
@@ -11015,22 +11015,22 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>6823c91b81f9dd0429e625ac</t>
+          <t>66cfa0f08be9a7041ad309f9</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Redondo</t>
+          <t>Jon Martín</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
@@ -11042,22 +11042,22 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>68a1066311d65103ec0070ef</t>
+          <t>6823c91b81f9dd0429e625ac</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>El-Abdellaoui</t>
+          <t>Redondo</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
@@ -11069,22 +11069,22 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>69b6fc4a1c66b403a1223d3d</t>
+          <t>68a1066311d65103ec0070ef</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Espart</t>
+          <t>El-Abdellaoui</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
@@ -11096,17 +11096,17 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>6a43e860e284b949d26e1c3c</t>
+          <t>69b6fc4a1c66b403a1223d3d</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grimaldo </t>
+          <t>Espart</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
@@ -11123,22 +11123,22 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>6a621c32c6d839058e965748</t>
+          <t>6a43e860e284b949d26e1c3c</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Adeyemi</t>
+          <t xml:space="preserve">Grimaldo </t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
@@ -11150,22 +11150,22 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>58cd754bafa5feac0520edda</t>
+          <t>6a621c32c6d839058e965748</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Guridi</t>
+          <t>Adeyemi</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
@@ -11177,22 +11177,22 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>59c7ab546c064c993bc73462</t>
+          <t>58cd754bafa5feac0520edda</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Luiz Felipe</t>
+          <t>Guridi</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
@@ -11204,22 +11204,22 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>594ad95d4ba3892d2226454c</t>
+          <t>59c7ab546c064c993bc73462</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Bernardo Silva</t>
+          <t>Luiz Felipe</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
@@ -11231,17 +11231,17 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>5cb344adaa68df0442669528</t>
+          <t>594ad95d4ba3892d2226454c</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Barrenetxea</t>
+          <t>Bernardo Silva</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
@@ -11258,12 +11258,12 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>59a9a9027d26b96314916033</t>
+          <t>5cb344adaa68df0442669528</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Guedes</t>
+          <t>Barrenetxea</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -11273,7 +11273,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
@@ -11285,22 +11285,22 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>5e2b73e8a7992b52c0641b93</t>
+          <t>59a9a9027d26b96314916033</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Manu Hernando</t>
+          <t>Guedes</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
@@ -11312,22 +11312,22 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>5b7864b259b3992b14aa4bc0</t>
+          <t>5e2b73e8a7992b52c0641b93</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Puado</t>
+          <t>Manu Hernando</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
@@ -11339,22 +11339,22 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>5f14b970f8e4ae03c1f96475</t>
+          <t>5b7864b259b3992b14aa4bc0</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Aimar Oroz</t>
+          <t>Puado</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
@@ -11366,22 +11366,22 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>5f75f6ff5efb030404be8b77</t>
+          <t>5f14b970f8e4ae03c1f96475</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Lookman</t>
+          <t>Aimar Oroz</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
@@ -11393,22 +11393,22 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>5f78e79033215d0412a634a7</t>
+          <t>5f75f6ff5efb030404be8b77</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Larrubia</t>
+          <t>Lookman</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
@@ -11420,17 +11420,17 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>601869861554ce07d665766f</t>
+          <t>5f78e79033215d0412a634a7</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Germán Valera</t>
+          <t>Larrubia</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
@@ -11447,22 +11447,22 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>60ed485214bb466048d3a5db</t>
+          <t>601869861554ce07d665766f</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Areso</t>
+          <t>Germán Valera</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
@@ -11474,17 +11474,17 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>607b5df9e292620d106cbb8e</t>
+          <t>60ed485214bb466048d3a5db</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Chust</t>
+          <t>Areso</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
@@ -11501,22 +11501,22 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>610ab7f51a405a604ca8c374</t>
+          <t>607b5df9e292620d106cbb8e</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Moleiro</t>
+          <t>Chust</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
@@ -11528,17 +11528,17 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>611e6d65c6657008542a1453</t>
+          <t>610ab7f51a405a604ca8c374</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Raúl Moro</t>
+          <t>Moleiro</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
@@ -11555,17 +11555,17 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>61996290d61a5d094f43a4bd</t>
+          <t>611e6d65c6657008542a1453</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Ilias Akhomach</t>
+          <t>Raúl Moro</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
@@ -11582,22 +11582,22 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>61c0eb88278f443e1e5d6a71</t>
+          <t>61996290d61a5d094f43a4bd</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Pubill</t>
+          <t>Ilias Akhomach</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
@@ -11609,17 +11609,17 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>62b31101deea5c2d8c81fdf5</t>
+          <t>61c0eb88278f443e1e5d6a71</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Dela</t>
+          <t>Pubill</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
@@ -11636,17 +11636,17 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>62e0f3d5fbbaa82d719997a2</t>
+          <t>62b31101deea5c2d8c81fdf5</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Quagliata</t>
+          <t>Dela</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
@@ -11663,17 +11663,17 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>62e58d3e11f4242dbd72531a</t>
+          <t>62e0f3d5fbbaa82d719997a2</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>José Salinas</t>
+          <t>Quagliata</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
@@ -11690,22 +11690,22 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>62ee482f2f093467dc60108e</t>
+          <t>62e58d3e11f4242dbd72531a</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Pablo Ibáñez</t>
+          <t>José Salinas</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
@@ -11717,17 +11717,17 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>630d3c68b640225ddc5861c9</t>
+          <t>62ee482f2f093467dc60108e</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Fran Pérez</t>
+          <t>Pablo Ibáñez</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
@@ -11744,17 +11744,17 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>635d5731fab08a089c78801c</t>
+          <t>630d3c68b640225ddc5861c9</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Pablo Barrios</t>
+          <t>Fran Pérez</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
@@ -11771,22 +11771,22 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>64d2b9156167273d0ccc5c4f</t>
+          <t>635d5731fab08a089c78801c</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Facundo González</t>
+          <t>Pablo Barrios</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
@@ -11798,22 +11798,22 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>6595c864840719702ac42c2a</t>
+          <t>64d2b9156167273d0ccc5c4f</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Hugo Álvarez</t>
+          <t>Facundo González</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
@@ -11825,22 +11825,22 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>65ac4fa5fa23880455a78f95</t>
+          <t>6595c864840719702ac42c2a</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Aramburu</t>
+          <t>Hugo Álvarez</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
@@ -11852,22 +11852,22 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>65988cd903b798703d8cc061</t>
+          <t>65ac4fa5fa23880455a78f95</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Buchanan</t>
+          <t>Aramburu</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
@@ -11879,22 +11879,22 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>65db9c727da3ff03e6654f00</t>
+          <t>65988cd903b798703d8cc061</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Arguibide</t>
+          <t>Buchanan</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
@@ -11906,22 +11906,22 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>65a14cffd9c62803f70f8509</t>
+          <t>65db9c727da3ff03e6654f00</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Isaac Romero</t>
+          <t>Arguibide</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
@@ -11933,22 +11933,22 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>6623fd0e5d937903d96ecca1</t>
+          <t>65a14cffd9c62803f70f8509</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Cabello</t>
+          <t>Isaac Romero</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
@@ -11960,22 +11960,22 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>66453408943e1536068fa651</t>
+          <t>6623fd0e5d937903d96ecca1</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Risco</t>
+          <t>Cabello</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
@@ -11987,22 +11987,22 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>66a3cafd9e452303b3fc0b5e</t>
+          <t>66453408943e1536068fa651</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>A. Osorio</t>
+          <t>Risco</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
@@ -12014,22 +12014,22 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>665ced2c03b5e9046aff4b19</t>
+          <t>66a3cafd9e452303b3fc0b5e</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Bauza</t>
+          <t>A. Osorio</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
@@ -12041,17 +12041,17 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>66b6a02fe0157a03f87fcb94</t>
+          <t>665ced2c03b5e9046aff4b19</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Gorrotxategi</t>
+          <t>Bauza</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
@@ -12068,17 +12068,17 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>666b0e4336df000455d656d4</t>
+          <t>66b6a02fe0157a03f87fcb94</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Christantus Uche</t>
+          <t>Gorrotxategi</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
@@ -12095,22 +12095,22 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>66802cdbfd03ab41756b1dc9</t>
+          <t>666b0e4336df000455d656d4</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Dani Barcia</t>
+          <t>Christantus Uche</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
@@ -12122,17 +12122,17 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>66d0a0d48be9a7041ad30d08</t>
+          <t>66802cdbfd03ab41756b1dc9</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Egiluz</t>
+          <t>Dani Barcia</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
@@ -12149,22 +12149,22 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>6780ea6d98d6a37581d90469</t>
+          <t>66d0a0d48be9a7041ad30d08</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Vargas</t>
+          <t>Egiluz</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
@@ -12176,22 +12176,22 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>66a9874cce303803d6f77525</t>
+          <t>6780ea6d98d6a37581d90469</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Yago Santiago</t>
+          <t>Vargas</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
@@ -12203,22 +12203,22 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>682893686f9b99317afd9034</t>
+          <t>66a9874cce303803d6f77525</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>F. Cardoso</t>
+          <t>Yago Santiago</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
@@ -12230,22 +12230,22 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>66c5102b8be9a7041ad2df88</t>
+          <t>682893686f9b99317afd9034</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Luiz Junior</t>
+          <t>F. Cardoso</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
@@ -12257,22 +12257,22 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>6865a9767775a433449e9c85</t>
+          <t>66c5102b8be9a7041ad2df88</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Noubi</t>
+          <t>Luiz Junior</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
@@ -12284,22 +12284,22 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>66d2486c099be403f1da8033</t>
+          <t>6865a9767775a433449e9c85</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Óskarsson</t>
+          <t>Noubi</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
@@ -12311,22 +12311,22 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>6884c2ae19c279041887fa84</t>
+          <t>66d2486c099be403f1da8033</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Valentín Gómez</t>
+          <t>Óskarsson</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
@@ -12338,22 +12338,22 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>679d3d34fdee6403d89449fe</t>
+          <t>6884c2ae19c279041887fa84</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Eddahchouri</t>
+          <t>Valentín Gómez</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
@@ -12365,22 +12365,22 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>68ebfeadaff4d55004ae1572</t>
+          <t>679d3d34fdee6403d89449fe</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Rafita</t>
+          <t>Eddahchouri</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
@@ -12392,22 +12392,22 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>67eeb84cb5d12f043f14e638</t>
+          <t>68ebfeadaff4d55004ae1572</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Fran González</t>
+          <t>Rafita</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
@@ -12419,22 +12419,22 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>68c735dbd4204b55b4125678</t>
+          <t>67eeb84cb5d12f043f14e638</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Roony</t>
+          <t>Fran González</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
@@ -12446,22 +12446,22 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>697bdf4c8d994403fc68fa11</t>
+          <t>68c735dbd4204b55b4125678</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Freeman</t>
+          <t>Roony</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
@@ -12473,22 +12473,22 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>6a4d1b4e2ae0d649eac3a152</t>
+          <t>697bdf4c8d994403fc68fa11</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Bernal</t>
+          <t>Freeman</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
@@ -12500,17 +12500,17 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>594d11088a928dbb0555e5a6</t>
+          <t>6a4d1b4e2ae0d649eac3a152</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Fede Valverde</t>
+          <t>Bernal</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
@@ -12527,17 +12527,17 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>5a2d6f2fd168259b3ede4aef</t>
+          <t>594d11088a928dbb0555e5a6</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Aitor Ruibal</t>
+          <t>Fede Valverde</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
@@ -12554,22 +12554,22 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>5c03bd490f4a903b890cd3da</t>
+          <t>5a2d6f2fd168259b3ede4aef</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Le Normand</t>
+          <t>Aitor Ruibal</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E450" t="inlineStr">
@@ -12581,17 +12581,17 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>5989a4391f9fb9af4ba1b806</t>
+          <t>5c03bd490f4a903b890cd3da</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Calero</t>
+          <t>Le Normand</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
@@ -12608,17 +12608,17 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>5f8b0f52406daa4fc599cfa0</t>
+          <t>5989a4391f9fb9af4ba1b806</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Carreira</t>
+          <t>Calero</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
@@ -12635,17 +12635,17 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>60b416c715f5654650f8e413</t>
+          <t>5f8b0f52406daa4fc599cfa0</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Sergi Cardona</t>
+          <t>Carreira</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
@@ -12662,22 +12662,22 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>5a23f0b68a9f96c2332504ab</t>
+          <t>60b416c715f5654650f8e413</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Raba</t>
+          <t>Sergi Cardona</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
@@ -12689,22 +12689,22 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>60dec77388c3b1602f5b3ae6</t>
+          <t>5a23f0b68a9f96c2332504ab</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Konaté</t>
+          <t>Raba</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
@@ -12716,22 +12716,22 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>5ac29d32c8bf976d1c180107</t>
+          <t>60dec77388c3b1602f5b3ae6</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Hugo Duro</t>
+          <t>Konaté</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
@@ -12743,17 +12743,17 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>61122ac42806395bcad477f0</t>
+          <t>5ac29d32c8bf976d1c180107</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Brugué</t>
+          <t>Hugo Duro</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
@@ -12770,22 +12770,22 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>5d0220e0167d9e5eb611db94</t>
+          <t>61122ac42806395bcad477f0</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Pol Lozano</t>
+          <t>Brugué</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E458" t="inlineStr">
@@ -12797,17 +12797,17 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>612e5dd7c44d9506f10f8fed</t>
+          <t>5d0220e0167d9e5eb611db94</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Camavinga</t>
+          <t>Pol Lozano</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
@@ -12824,22 +12824,22 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>5d430c1e2099e47b0f3d7650</t>
+          <t>612e5dd7c44d9506f10f8fed</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>Danjuma</t>
+          <t>Camavinga</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
@@ -12851,12 +12851,12 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>614f52757bf8f60892e55d4a</t>
+          <t>5d430c1e2099e47b0f3d7650</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Jesús Vázquez</t>
+          <t>Danjuma</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
@@ -12866,7 +12866,7 @@
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E461" t="inlineStr">
@@ -12878,22 +12878,22 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>61b51da6d1dcc206d030bacc</t>
+          <t>614f52757bf8f60892e55d4a</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Dani Lorenzo</t>
+          <t>Jesús Vázquez</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
@@ -12905,22 +12905,22 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>6089b8ace0c69806f612a3d4</t>
+          <t>61b51da6d1dcc206d030bacc</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Nico Williams</t>
+          <t>Dani Lorenzo</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E463" t="inlineStr">
@@ -12932,22 +12932,22 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>62b30b7011f4242dbd7252b0</t>
+          <t>6089b8ace0c69806f612a3d4</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Mantilla</t>
+          <t>Nico Williams</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
@@ -12959,22 +12959,22 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>610174c4bc32266071ced17a</t>
+          <t>62b30b7011f4242dbd7252b0</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>Oriol Rey</t>
+          <t>Mantilla</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
@@ -12986,22 +12986,22 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>62f826f93355b0168987308d</t>
+          <t>610174c4bc32266071ced17a</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Abqar</t>
+          <t>Oriol Rey</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
@@ -13013,22 +13013,22 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>61122a78c7c51f5b9a6ca7c4</t>
+          <t>62f826f93355b0168987308d</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>Pepelu</t>
+          <t>Abqar</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E467" t="inlineStr">
@@ -13040,12 +13040,12 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>630d3bceb4ad355e01bea95f</t>
+          <t>61122a78c7c51f5b9a6ca7c4</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>Diego López</t>
+          <t>Pepelu</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -13055,7 +13055,7 @@
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E468" t="inlineStr">
@@ -13067,22 +13067,22 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>61184f3ad8a84f5bb9a7fe9d</t>
+          <t>630d3bceb4ad355e01bea95f</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>Dumfries</t>
+          <t>Diego López</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
@@ -13094,17 +13094,17 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>63375e14c376ff465d2a5af7</t>
+          <t>61184f3ad8a84f5bb9a7fe9d</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>Aitor Paredes</t>
+          <t>Dumfries</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
@@ -13121,17 +13121,17 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>614204ec48f6a015444ac7df</t>
+          <t>63375e14c376ff465d2a5af7</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Balde</t>
+          <t>Aitor Paredes</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
@@ -13148,17 +13148,17 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>64516ff73917190401517dfb</t>
+          <t>614204ec48f6a015444ac7df</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Herrando</t>
+          <t>Balde</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
@@ -13175,22 +13175,22 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>62adceb2b2a1132d77c95779</t>
+          <t>64516ff73917190401517dfb</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Swedberg</t>
+          <t>Herrando</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
@@ -13202,22 +13202,22 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>64a6fcb014cd337373737ba9</t>
+          <t>62adceb2b2a1132d77c95779</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Güler</t>
+          <t>Swedberg</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
@@ -13229,17 +13229,17 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>62ae4ce2c057ca2d85a004e2</t>
+          <t>64a6fcb014cd337373737ba9</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Hjulmand</t>
+          <t>Güler</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
@@ -13256,22 +13256,22 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>655be3da0cc5192b1a75785c</t>
+          <t>62ae4ce2c057ca2d85a004e2</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Xavi Grande</t>
+          <t>Hjulmand</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
@@ -13283,22 +13283,22 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>630e1e745328c70716999d1d</t>
+          <t>655be3da0cc5192b1a75785c</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Antony</t>
+          <t>Xavi Grande</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
@@ -13310,22 +13310,22 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>631ca92becf9a206fe07abea</t>
+          <t>630e1e745328c70716999d1d</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Kike Salas</t>
+          <t>Antony</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
@@ -13337,17 +13337,17 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>65ad5e596519630480ca1cf7</t>
+          <t>631ca92becf9a206fe07abea</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Cubarsí</t>
+          <t>Kike Salas</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
@@ -13364,22 +13364,22 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>666741233b1ffd0457e2b565</t>
+          <t>65ad5e596519630480ca1cf7</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Djaló</t>
+          <t>Cubarsí</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
@@ -13391,22 +13391,22 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>65ba7f36d859840e31ca03fe</t>
+          <t>666741233b1ffd0457e2b565</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Hugo Novoa</t>
+          <t>Djaló</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
@@ -13418,22 +13418,22 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>666890c0ac5cca0443fd54dd</t>
+          <t>65ba7f36d859840e31ca03fe</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>Endrick</t>
+          <t>Hugo Novoa</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
@@ -13445,12 +13445,12 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>66659f6d36df000455d656bf</t>
+          <t>666890c0ac5cca0443fd54dd</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>Mbappé</t>
+          <t>Endrick</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
@@ -13472,22 +13472,22 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>66802e7e654982413588730f</t>
+          <t>66659f6d36df000455d656bf</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>Rubén López</t>
+          <t>Mbappé</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
@@ -13499,22 +13499,22 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>668015b50ab8ba417f327194</t>
+          <t>66802e7e654982413588730f</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>Roberto Fernández</t>
+          <t>Rubén López</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
@@ -13526,12 +13526,12 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>66905806702b9203b99a1357</t>
+          <t>668015b50ab8ba417f327194</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>Álex Calatrava</t>
+          <t>Roberto Fernández</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
@@ -13541,7 +13541,7 @@
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">
@@ -13553,17 +13553,17 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>66802dd799f9bf415ff4350c</t>
+          <t>66905806702b9203b99a1357</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>Diego Villares</t>
+          <t>Álex Calatrava</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
@@ -13580,12 +13580,12 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>66802fd539012a413c5d995f</t>
+          <t>66802dd799f9bf415ff4350c</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Yeremay Hernández</t>
+          <t>Diego Villares</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
@@ -13595,7 +13595,7 @@
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E488" t="inlineStr">
@@ -13607,22 +13607,22 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>66f98191043342085bbcc7ce</t>
+          <t>66802fd539012a413c5d995f</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>Peio Canales</t>
+          <t>Yeremay Hernández</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
@@ -13634,22 +13634,22 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>66a3d3797fc6ff03fb06facf</t>
+          <t>66f98191043342085bbcc7ce</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Boselli</t>
+          <t>Peio Canales</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">
@@ -13661,17 +13661,17 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>6865791adf31913331fecaf7</t>
+          <t>66a3d3797fc6ff03fb06facf</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Hartman</t>
+          <t>Boselli</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
@@ -13688,22 +13688,22 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>66c72a0476de1f03e6d2b55a</t>
+          <t>6865791adf31913331fecaf7</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Gueye</t>
+          <t>Hartman</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E492" t="inlineStr">
@@ -13715,22 +13715,22 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>688318293777f6041274556c</t>
+          <t>66c72a0476de1f03e6d2b55a</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Hancko</t>
+          <t>Gueye</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
@@ -13742,22 +13742,22 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>6861bef57775a433449e9581</t>
+          <t>688318293777f6041274556c</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Jutglà</t>
+          <t>Hancko</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E494" t="inlineStr">
@@ -13769,17 +13769,17 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>6861cd7eca97b13338e6c16d</t>
+          <t>6861bef57775a433449e9581</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Marcos Fernández</t>
+          <t>Jutglà</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
@@ -13796,22 +13796,22 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>68a234d9a9a91a0415a3788b</t>
+          <t>6861cd7eca97b13338e6c16d</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>Rego</t>
+          <t>Marcos Fernández</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E496" t="inlineStr">
@@ -13823,22 +13823,22 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>68780dec5c7211044690a3a9</t>
+          <t>68a234d9a9a91a0415a3788b</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>Yusi</t>
+          <t>Rego</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E497" t="inlineStr">
@@ -13850,17 +13850,17 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>68adbb77d1d08d1c1f1228ce</t>
+          <t>68780dec5c7211044690a3a9</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Hinojo</t>
+          <t>Yusi</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
@@ -13877,22 +13877,22 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>68b486b8882e4a05b2d43111</t>
+          <t>68adbb77d1d08d1c1f1228ce</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Román</t>
+          <t>Hinojo</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
@@ -13904,22 +13904,22 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>6960f922cd59040409e50fd9</t>
+          <t>68b486b8882e4a05b2d43111</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Guliashvili</t>
+          <t>Román</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E500" t="inlineStr">
@@ -13931,17 +13931,17 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>6946c6f73a8ebd03f25fc9a3</t>
+          <t>6960f922cd59040409e50fd9</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Nsongo</t>
+          <t>Guliashvili</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
@@ -13958,22 +13958,22 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>696e8199368a5803c07f3bc1</t>
+          <t>6946c6f73a8ebd03f25fc9a3</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Eriksson</t>
+          <t>Nsongo</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
@@ -13985,22 +13985,22 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>69752256a68dd603be29f508</t>
+          <t>696e8199368a5803c07f3bc1</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Hierro</t>
+          <t>Eriksson</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E503" t="inlineStr">
@@ -14012,22 +14012,22 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>69890d253b0d1b03ea61084c</t>
+          <t>69752256a68dd603be29f508</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>Cestero</t>
+          <t>Hierro</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
@@ -14039,22 +14039,22 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>6a358ea99542a303bf19bf7a</t>
+          <t>69890d253b0d1b03ea61084c</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Sangante</t>
+          <t>Cestero</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
@@ -14066,22 +14066,22 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>5d43ec6312ba017aeb3ad5ae</t>
+          <t>6a358ea99542a303bf19bf7a</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>Sancet</t>
+          <t>Sangante</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E506" t="inlineStr">
@@ -14093,22 +14093,22 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>5851e8da3defeb5375f2cb30</t>
+          <t>5d43ec6312ba017aeb3ad5ae</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>Trent</t>
+          <t>Sancet</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E507" t="inlineStr">
@@ -14120,22 +14120,22 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>5d58321f489a8e5316ca89d6</t>
+          <t>5851e8da3defeb5375f2cb30</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>Iker Losada</t>
+          <t>Trent</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E508" t="inlineStr">
@@ -14147,17 +14147,17 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>59c2d829bd61e7f10c49a9b6</t>
+          <t>5d58321f489a8e5316ca89d6</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>Edu Expósito</t>
+          <t>Iker Losada</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D509" t="inlineStr">
@@ -14174,22 +14174,22 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>5da39ad5b8e82e5c69ab75f9</t>
+          <t>59c2d829bd61e7f10c49a9b6</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>Valles</t>
+          <t>Edu Expósito</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E510" t="inlineStr">
@@ -14201,12 +14201,12 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>5a81f13ce3c1953064f782e0</t>
+          <t>5da39ad5b8e82e5c69ab75f9</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>Junior Firpo</t>
+          <t>Valles</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
@@ -14216,7 +14216,7 @@
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E511" t="inlineStr">
@@ -14228,17 +14228,17 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>5efa4e35ee5a640417710119</t>
+          <t>5a81f13ce3c1953064f782e0</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>Jon Pacheco</t>
+          <t>Junior Firpo</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D512" t="inlineStr">
@@ -14255,22 +14255,22 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>5b33408c744d2a591d3e566e</t>
+          <t>5efa4e35ee5a640417710119</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>Vinícius</t>
+          <t>Jon Pacheco</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E513" t="inlineStr">
@@ -14282,22 +14282,22 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>60d73641b7fb6703d3e21ba8</t>
+          <t>5b33408c744d2a591d3e566e</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>Olasagasti</t>
+          <t>Vinícius</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E514" t="inlineStr">
@@ -14309,22 +14309,22 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>5bd4d4dd2549d75a2c65508e</t>
+          <t>60d73641b7fb6703d3e21ba8</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>Julián Álvarez</t>
+          <t>Olasagasti</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E515" t="inlineStr">
@@ -14336,22 +14336,22 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>60e72704dfb903607d1f7d87</t>
+          <t>5bd4d4dd2549d75a2c65508e</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>Dituro</t>
+          <t>Julián Álvarez</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E516" t="inlineStr">
@@ -14363,22 +14363,22 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>61228f14bee4ec08574d99bf</t>
+          <t>60e72704dfb903607d1f7d87</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>Haitam</t>
+          <t>Dituro</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E517" t="inlineStr">
@@ -14390,22 +14390,22 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>5f4e59209209ce03d8236b09</t>
+          <t>61228f14bee4ec08574d99bf</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>Fran García</t>
+          <t>Haitam</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E518" t="inlineStr">
@@ -14417,17 +14417,17 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>61bd0e030d81623e3a2b0f28</t>
+          <t>5f4e59209209ce03d8236b09</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>Rubén Sánchez</t>
+          <t>Fran García</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D519" t="inlineStr">
@@ -14444,22 +14444,22 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>61dcacebb6d6540425b75dce</t>
+          <t>61bd0e030d81623e3a2b0f28</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>Joan García</t>
+          <t>Rubén Sánchez</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E520" t="inlineStr">
@@ -14471,22 +14471,22 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>62b3132cb2a1132d77c95799</t>
+          <t>61dcacebb6d6540425b75dce</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>Arana</t>
+          <t>Joan García</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E521" t="inlineStr">
@@ -14498,12 +14498,12 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>64d3c4746167273d0ccc5c52</t>
+          <t>62b3132cb2a1132d77c95799</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>Pablo Ramón</t>
+          <t>Arana</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
@@ -14513,7 +14513,7 @@
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E522" t="inlineStr">
@@ -14525,22 +14525,22 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>62c3721bc057ca2d85a00512</t>
+          <t>64d3c4746167273d0ccc5c52</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>Giuliano Simeone</t>
+          <t>Pablo Ramón</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E523" t="inlineStr">
@@ -14552,17 +14552,17 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>64ea79b9b1931503ca17ef44</t>
+          <t>62c3721bc057ca2d85a00512</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>Dani Requena</t>
+          <t>Giuliano Simeone</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D524" t="inlineStr">
@@ -14579,22 +14579,22 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>632f6e29e25c770b961eabe9</t>
+          <t>64ea79b9b1931503ca17ef44</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>Murillo</t>
+          <t>Dani Requena</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E525" t="inlineStr">
@@ -14606,17 +14606,17 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>632f6f28d2f4c20bd75d484b</t>
+          <t>632f6e29e25c770b961eabe9</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>Carlos Romero</t>
+          <t>Murillo</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="D526" t="inlineStr">
@@ -14633,22 +14633,22 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>64f4d4b99318fc03ee16e82d</t>
+          <t>632f6f28d2f4c20bd75d484b</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>Amatucci</t>
+          <t>Carlos Romero</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E527" t="inlineStr">
@@ -14660,17 +14660,17 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>643c697b471fc403f43359d6</t>
+          <t>64f4d4b99318fc03ee16e82d</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>Javi Guerra</t>
+          <t>Amatucci</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D528" t="inlineStr">
@@ -14687,17 +14687,17 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>66ccfe37683d1203dc8a58b3</t>
+          <t>643c697b471fc403f43359d6</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>Alfon</t>
+          <t>Javi Guerra</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D529" t="inlineStr">
@@ -14714,22 +14714,22 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>66841f9cd8d63f414aab7434</t>
+          <t>66ccfe37683d1203dc8a58b3</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>Pelayo</t>
+          <t>Alfon</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E530" t="inlineStr">
@@ -14741,22 +14741,22 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>6806b68446e3f90444f1d995</t>
+          <t>66841f9cd8d63f414aab7434</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>Rafa Rodríguez</t>
+          <t>Pelayo</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E531" t="inlineStr">
@@ -14768,22 +14768,22 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>66b8ed0a702b9203b99a1705</t>
+          <t>6806b68446e3f90444f1d995</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>Hugo Rincón</t>
+          <t>Rafa Rodríguez</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E532" t="inlineStr">
@@ -14795,22 +14795,22 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>66c11ee4b5741f1a24b14824</t>
+          <t>66b8ed0a702b9203b99a1705</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>Otorbi</t>
+          <t>Hugo Rincón</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E533" t="inlineStr">
@@ -14822,22 +14822,22 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>66c7c242f119260402e25f8f</t>
+          <t>66c11ee4b5741f1a24b14824</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>Logan Costa</t>
+          <t>Otorbi</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E534" t="inlineStr">
@@ -14849,22 +14849,22 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>678bea540e424b7573dc9cf3</t>
+          <t>66c7c242f119260402e25f8f</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Adrián Niño</t>
+          <t>Logan Costa</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E535" t="inlineStr">
@@ -14876,22 +14876,22 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>696c1bb8af58fa040efb6d15</t>
+          <t>678bea540e424b7573dc9cf3</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Zaid Romero</t>
+          <t>Adrián Niño</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="D536" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E536" t="inlineStr">
@@ -14903,22 +14903,22 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>67d4acc7fb012703e17d1dc5</t>
+          <t>696c1bb8af58fa040efb6d15</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Adrián R.</t>
+          <t>Zaid Romero</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E537" t="inlineStr">
@@ -14930,12 +14930,12 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>697e90b3ff715b03c5df8278</t>
+          <t>67d4acc7fb012703e17d1dc5</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Koski</t>
+          <t>Adrián R.</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
@@ -14945,7 +14945,7 @@
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E538" t="inlineStr">
@@ -14957,22 +14957,22 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>69810c427602e303cbed6a3e</t>
+          <t>697e90b3ff715b03c5df8278</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Obed Vargas</t>
+          <t>Koski</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E539" t="inlineStr">
@@ -14984,17 +14984,17 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>688fbfc45c7211044690a3d3</t>
+          <t>69810c427602e303cbed6a3e</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>Selu Diallo</t>
+          <t>Obed Vargas</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D540" t="inlineStr">
@@ -15011,17 +15011,17 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>6a4d1c7ce284b949d26e34f5</t>
+          <t>688fbfc45c7211044690a3d3</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>Sato</t>
+          <t>Selu Diallo</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D541" t="inlineStr">
@@ -15038,22 +15038,22 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>6988af503b0d1b03ea60fa11</t>
+          <t>6a4d1c7ce284b949d26e34f5</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>Aitor Mañas</t>
+          <t>Sato</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E542" t="inlineStr">
@@ -15065,22 +15065,22 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>6a39255e9b413b03b20c1fd5</t>
+          <t>6988af503b0d1b03ea60fa11</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>De Haas</t>
+          <t>Aitor Mañas</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E543" t="inlineStr">
@@ -15092,22 +15092,22 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>504e58bb4d8bec9a6700017a</t>
+          <t>6a39255e9b413b03b20c1fd5</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>Courtois</t>
+          <t>De Haas</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E544" t="inlineStr">
@@ -15119,22 +15119,22 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>5b43ab6e5c2992ae0bf69a35</t>
+          <t>504e58bb4d8bec9a6700017a</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>Gonzalo Villar</t>
+          <t>Courtois</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E545" t="inlineStr">
@@ -15146,22 +15146,22 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>51cb698301d64ad4700000bc</t>
+          <t>5b43ab6e5c2992ae0bf69a35</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>Szczesny</t>
+          <t>Gonzalo Villar</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E546" t="inlineStr">
@@ -15173,22 +15173,22 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>5c0eea87e3eca97d26f62cee</t>
+          <t>51cb698301d64ad4700000bc</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>Pedrosa</t>
+          <t>Szczesny</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E547" t="inlineStr">
@@ -15200,22 +15200,22 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>58e1616852a7d14c54bb26d3</t>
+          <t>5c0eea87e3eca97d26f62cee</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>Carles Aleñá</t>
+          <t>Pedrosa</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E548" t="inlineStr">
@@ -15227,12 +15227,12 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>5c8bf51dc84b6a5140cdd554</t>
+          <t>58e1616852a7d14c54bb26d3</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>Guevara</t>
+          <t>Carles Aleñá</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
@@ -15254,22 +15254,22 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>5989a27fd094c1ec4bdbf741</t>
+          <t>5c8bf51dc84b6a5140cdd554</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>Unai Núñez</t>
+          <t>Guevara</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E550" t="inlineStr">
@@ -15281,22 +15281,22 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>5d430d22b1b9c77b1c9551f7</t>
+          <t>5989a27fd094c1ec4bdbf741</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>Nicolas Pépé</t>
+          <t>Unai Núñez</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E551" t="inlineStr">
@@ -15308,22 +15308,22 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>59ff3b0329d7bf994b9e01f0</t>
+          <t>5d430d22b1b9c77b1c9551f7</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>Tenaglia</t>
+          <t>Nicolas Pépé</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E552" t="inlineStr">
@@ -15335,17 +15335,17 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>5f32e17633a68903ecffbd1f</t>
+          <t>59ff3b0329d7bf994b9e01f0</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>Vivian</t>
+          <t>Tenaglia</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D553" t="inlineStr">
@@ -15362,22 +15362,22 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>5a639998e2a0fd3424128d06</t>
+          <t>5f32e17633a68903ecffbd1f</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>Brahim Díaz</t>
+          <t>Vivian</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E554" t="inlineStr">
@@ -15389,22 +15389,22 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>5fc1512d94ce070e962e3a3c</t>
+          <t>5a639998e2a0fd3424128d06</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>Cárdenas</t>
+          <t>Brahim Díaz</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E555" t="inlineStr">
@@ -15416,22 +15416,22 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>5b958b5a57a45c624cf0747d</t>
+          <t>5fc1512d94ce070e962e3a3c</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>Andrés Martín</t>
+          <t>Cárdenas</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E556" t="inlineStr">
@@ -15443,22 +15443,22 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>5c437caeb40d97040e679cb2</t>
+          <t>5b958b5a57a45c624cf0747d</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>Joaquín Muñoz</t>
+          <t>Andrés Martín</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E557" t="inlineStr">
@@ -15470,22 +15470,22 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>617db824fca9f703e07b2a81</t>
+          <t>5c437caeb40d97040e679cb2</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>Abde Ezzalzouli</t>
+          <t>Joaquín Muñoz</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E558" t="inlineStr">
@@ -15497,17 +15497,17 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>5d134f035af255065129d598</t>
+          <t>617db824fca9f703e07b2a81</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>Nteka</t>
+          <t>Abde Ezzalzouli</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D559" t="inlineStr">
@@ -15524,22 +15524,22 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>62b30b04d367e02dade46984</t>
+          <t>5d134f035af255065129d598</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>Iñigo Sainz</t>
+          <t>Nteka</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E560" t="inlineStr">
@@ -15551,22 +15551,22 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>5e23437d616e7d03ba5dc21c</t>
+          <t>62b30b04d367e02dade46984</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>Gordon</t>
+          <t>Iñigo Sainz</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E561" t="inlineStr">
@@ -15578,22 +15578,22 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>602833759c7d2b6c2de127f5</t>
+          <t>5e23437d616e7d03ba5dc21c</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>Ilaix Moriba</t>
+          <t>Gordon</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D562" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E562" t="inlineStr">
@@ -15605,22 +15605,22 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>63cdb1fff41df804fa60e6f1</t>
+          <t>602833759c7d2b6c2de127f5</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>Castrín</t>
+          <t>Ilaix Moriba</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E563" t="inlineStr">
@@ -15632,22 +15632,22 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>607325f27b19b30c4fb34081</t>
+          <t>63cdb1fff41df804fa60e6f1</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>Urko González</t>
+          <t>Castrín</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D564" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E564" t="inlineStr">
@@ -15659,17 +15659,17 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>63d8eb7b1d17ae5aff1f4c52</t>
+          <t>607325f27b19b30c4fb34081</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>Gueye</t>
+          <t>Urko González</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D565" t="inlineStr">
@@ -15686,17 +15686,17 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>63fd2d48e13c195af1f7112f</t>
+          <t>63d8eb7b1d17ae5aff1f4c52</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>Terrats</t>
+          <t>Gueye</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D566" t="inlineStr">
@@ -15713,22 +15713,22 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>630a8dadb3e9b206bc1bb9c4</t>
+          <t>63fd2d48e13c195af1f7112f</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>Carmona</t>
+          <t>Terrats</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E567" t="inlineStr">
@@ -15740,17 +15740,17 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>64a72d1f537887736c506e33</t>
+          <t>630a8dadb3e9b206bc1bb9c4</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>Mouriño</t>
+          <t>Carmona</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D568" t="inlineStr">
@@ -15767,17 +15767,17 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>654032293d123e329221f359</t>
+          <t>64a72d1f537887736c506e33</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>Alti</t>
+          <t>Mouriño</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D569" t="inlineStr">
@@ -15794,12 +15794,12 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>64b1c368b6533c3d21125718</t>
+          <t>654032293d123e329221f359</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>Mario Soriano</t>
+          <t>Alti</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
@@ -15809,7 +15809,7 @@
       </c>
       <c r="D570" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E570" t="inlineStr">
@@ -15821,22 +15821,22 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>65b56235a3176a0e0fdb8f74</t>
+          <t>64b1c368b6533c3d21125718</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>Héctor Fort</t>
+          <t>Mario Soriano</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D571" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E571" t="inlineStr">
@@ -15848,22 +15848,22 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>65b68e44017f760e15bff480</t>
+          <t>65b56235a3176a0e0fdb8f74</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>Jauregizar</t>
+          <t>Héctor Fort</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E572" t="inlineStr">
@@ -15875,22 +15875,22 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>66919efdc34e5603e02bfd43</t>
+          <t>65b68e44017f760e15bff480</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>Renato Veiga</t>
+          <t>Jauregizar</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E573" t="inlineStr">
@@ -15902,22 +15902,22 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>669e6b4f99e2e504052cbbe5</t>
+          <t>66919efdc34e5603e02bfd43</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>Álex Padilla</t>
+          <t>Renato Veiga</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E574" t="inlineStr">
@@ -15929,22 +15929,22 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>6689c4a399e2e504052caf27</t>
+          <t>669e6b4f99e2e504052cbbe5</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>Rosier</t>
+          <t>Álex Padilla</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E575" t="inlineStr">
@@ -15956,17 +15956,17 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>66c25f14b5741f1a24b155a4</t>
+          <t>6689c4a399e2e504052caf27</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>Barzic</t>
+          <t>Rosier</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D576" t="inlineStr">
@@ -15983,12 +15983,12 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>66c8333550cfa503c1736efc</t>
+          <t>66c25f14b5741f1a24b155a4</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>Diaby</t>
+          <t>Barzic</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
@@ -16010,17 +16010,17 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>679d3bc45efcdd03e54eee29</t>
+          <t>66c8333550cfa503c1736efc</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>Arnau Comas</t>
+          <t>Diaby</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D578" t="inlineStr">
@@ -16037,17 +16037,17 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>6795064560299f03fb5de648</t>
+          <t>679d3bc45efcdd03e54eee29</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>Ángel Ortiz</t>
+          <t>Arnau Comas</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D579" t="inlineStr">
@@ -16064,12 +16064,12 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>682920fc77ba5003ca4869ce</t>
+          <t>6795064560299f03fb5de648</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>Deossa</t>
+          <t>Ángel Ortiz</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
@@ -16079,7 +16079,7 @@
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E580" t="inlineStr">
@@ -16091,17 +16091,17 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>6866a4e8ca97b13338e6cd0a</t>
+          <t>682920fc77ba5003ca4869ce</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>Mikel Rodríguez</t>
+          <t>Deossa</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D581" t="inlineStr">
@@ -16118,22 +16118,22 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>6878cacd19c279041887fa6f</t>
+          <t>6866a4e8ca97b13338e6cd0a</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>Iturbe</t>
+          <t>Mikel Rodríguez</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E582" t="inlineStr">
@@ -16145,22 +16145,22 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>69a5ddd7cd2bdb03fcc07f8a</t>
+          <t>6878cacd19c279041887fa6f</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>Thiago Pitarch</t>
+          <t>Iturbe</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E583" t="inlineStr">
@@ -16172,22 +16172,22 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>68951bdfb2ec15040b6eee00</t>
+          <t>69a5ddd7cd2bdb03fcc07f8a</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>Fortuño</t>
+          <t>Thiago Pitarch</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E584" t="inlineStr">
@@ -16199,22 +16199,22 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>6a35ba801636ff03e132961e</t>
+          <t>68951bdfb2ec15040b6eee00</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>Gijselhart</t>
+          <t>Fortuño</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E585" t="inlineStr">

--- a/datos/maestros/md_jugadores.xlsx
+++ b/datos/maestros/md_jugadores.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E800"/>
+  <dimension ref="A1:E801"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8018,22 +8018,22 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>5767a067e854a6271e7ff173</t>
+          <t>655be3da0cc5192b1a75785c</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Toni Martínez</t>
+          <t>Xavi Grande</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -8045,17 +8045,17 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>5634f6a0268e529b04ff8c45</t>
+          <t>5767a067e854a6271e7ff173</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Borja Mayoral</t>
+          <t>Toni Martínez</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -8072,22 +8072,22 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>52079128fa700fba29000016</t>
+          <t>5634f6a0268e529b04ff8c45</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Pere Milla</t>
+          <t>Borja Mayoral</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -8099,22 +8099,22 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>5591624ea1736b3a42844561</t>
+          <t>52079128fa700fba29000016</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Villalibre</t>
+          <t>Pere Milla</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -8126,22 +8126,22 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>52017ff1cf55e01b3400002e</t>
+          <t>5591624ea1736b3a42844561</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Mandi</t>
+          <t>Villalibre</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -8153,17 +8153,17 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>57363a66ad212396073bce9f</t>
+          <t>52017ff1cf55e01b3400002e</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Zubeldia</t>
+          <t>Mandi</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -8180,22 +8180,22 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>5201061f19cbe478070000c6</t>
+          <t>57363a66ad212396073bce9f</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Sergio Herrera</t>
+          <t>Zubeldia</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -8207,17 +8207,17 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>5202890bd7a595bd3700007b</t>
+          <t>5201061f19cbe478070000c6</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t xml:space="preserve">Germán </t>
+          <t>Sergio Herrera</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -8234,17 +8234,17 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>5214d165dbf8b74f020000e3</t>
+          <t>5202890bd7a595bd3700007b</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Aitor Fernández</t>
+          <t xml:space="preserve">Germán </t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -8261,12 +8261,12 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>574dc94bb9278bf5518b1e7b</t>
+          <t>5214d165dbf8b74f020000e3</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Budimir</t>
+          <t>Aitor Fernández</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -8276,7 +8276,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -8288,22 +8288,22 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>5402cba8e8a4c9292a000287</t>
+          <t>574dc94bb9278bf5518b1e7b</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Christensen</t>
+          <t>Budimir</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -8315,17 +8315,17 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>50d2514b099731b00e02ee94</t>
+          <t>5402cba8e8a4c9292a000287</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Laporte</t>
+          <t>Christensen</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -8342,17 +8342,17 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>51b89bd5e401a15f2c000140</t>
+          <t>50d2514b099731b00e02ee94</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Cabrera</t>
+          <t>Laporte</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -8369,17 +8369,17 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>504f65024d8bec9a670005a6</t>
+          <t>51b89bd5e401a15f2c000140</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Ximo Navarro</t>
+          <t>Cabrera</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -8396,12 +8396,12 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>523473325a4ad28f01000014</t>
+          <t>504f65024d8bec9a670005a6</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Giménez</t>
+          <t>Ximo Navarro</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -8423,22 +8423,22 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>55b66bc6fe0ded1c22ebbd6d</t>
+          <t>523473325a4ad28f01000014</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Dmitrovic</t>
+          <t>Giménez</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -8450,22 +8450,22 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>520d1ce5a776cc826b000026</t>
+          <t>55b66bc6fe0ded1c22ebbd6d</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Lucas Torró</t>
+          <t>Dmitrovic</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -8477,22 +8477,22 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>525d4f895231f4d645000795</t>
+          <t>520d1ce5a776cc826b000026</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Iván Villar</t>
+          <t>Lucas Torró</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -8504,22 +8504,22 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>5442eeb84e1f41e97e000261</t>
+          <t>525d4f895231f4d645000795</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Bellerin</t>
+          <t>Iván Villar</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -8531,17 +8531,17 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>544dfb9b322ce8ed010002bf</t>
+          <t>5442eeb84e1f41e97e000261</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Djené</t>
+          <t>Bellerin</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -8558,22 +8558,22 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>56787538d0e498cf3e24cda6</t>
+          <t>544dfb9b322ce8ed010002bf</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Guruzeta</t>
+          <t>Djené</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -8585,22 +8585,22 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>522f8e353ce1ab673f00000b</t>
+          <t>56787538d0e498cf3e24cda6</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Bartra</t>
+          <t>Guruzeta</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -8612,22 +8612,22 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>522ccdebe10a44087f0000ec</t>
+          <t>522f8e353ce1ab673f00000b</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Unai López</t>
+          <t>Bartra</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -8639,17 +8639,17 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>504e58594d8bec9a67000106</t>
+          <t>522ccdebe10a44087f0000ec</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Galarreta</t>
+          <t>Unai López</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -8666,22 +8666,22 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>520d0d314386b4816b000029</t>
+          <t>504e58594d8bec9a67000106</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Alfonso Herrero</t>
+          <t>Galarreta</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -8693,22 +8693,22 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>51b895eae401a15f2c00012d</t>
+          <t>520d0d314386b4816b000029</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Moi Gómez</t>
+          <t>Alfonso Herrero</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -8720,17 +8720,17 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>504e58bb4d8bec9a67000187</t>
+          <t>51b895eae401a15f2c00012d</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Koke</t>
+          <t>Moi Gómez</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -8747,22 +8747,22 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>53df365ce5c94c6a08000203</t>
+          <t>504e58bb4d8bec9a67000187</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Kiko Femenía</t>
+          <t>Koke</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -8774,22 +8774,22 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>520243d0d7a595bd3700001f</t>
+          <t>53df365ce5c94c6a08000203</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Oblak</t>
+          <t>Kiko Femenía</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -8801,22 +8801,22 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>5676df0e008eb5c93e62f205</t>
+          <t>520243d0d7a595bd3700001f</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Sadiq Umar</t>
+          <t>Oblak</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -8828,12 +8828,12 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>520d201ca776cc826b000029</t>
+          <t>5676df0e008eb5c93e62f205</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Luis Rioja</t>
+          <t>Sadiq Umar</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -8843,7 +8843,7 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
@@ -8855,22 +8855,22 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>521a999b5865e5687000001c</t>
+          <t>520d201ca776cc826b000029</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t xml:space="preserve">David Soria </t>
+          <t>Luis Rioja</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -8882,22 +8882,22 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>5738fcf88179bfa8526e19ce</t>
+          <t>521a999b5865e5687000001c</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Sergi Canós</t>
+          <t xml:space="preserve">David Soria </t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -8909,22 +8909,22 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>51b9e593e401a15f2c00019f</t>
+          <t>5738fcf88179bfa8526e19ce</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Toljan</t>
+          <t>Sergi Canós</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -8936,22 +8936,22 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>51d71d02a7178a7654000017</t>
+          <t>51b9e593e401a15f2c00019f</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Aubameyang</t>
+          <t>Toljan</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
@@ -8963,22 +8963,22 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>5203972e2e80d2950b00016f</t>
+          <t>51d71d02a7178a7654000017</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>J. Musso</t>
+          <t>Aubameyang</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -8990,22 +8990,22 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>520d29408091fd886b000049</t>
+          <t>5203972e2e80d2950b00016f</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Mariano</t>
+          <t>J. Musso</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -9017,22 +9017,22 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>5590e248b804493642903cdc</t>
+          <t>520d29408091fd886b000049</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Remiro</t>
+          <t>Mariano</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -9044,22 +9044,22 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>53c61e5c3554a2ca66000014</t>
+          <t>5590e248b804493642903cdc</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Lejeune</t>
+          <t>Remiro</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -9071,22 +9071,22 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>52175e9470a79164260001a4</t>
+          <t>53c61e5c3554a2ca66000014</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Borja Iglesias</t>
+          <t>Lejeune</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -9098,22 +9098,22 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>5590e613b804493642903d44</t>
+          <t>52175e9470a79164260001a4</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Yeray</t>
+          <t>Borja Iglesias</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -9125,22 +9125,22 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>504f50c54d8bec9a670003d1</t>
+          <t>5590e613b804493642903d44</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Iago Aspas</t>
+          <t>Yeray</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -9152,22 +9152,22 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>505d8a247e438909310001c5</t>
+          <t>504f50c54d8bec9a670003d1</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Rubén García</t>
+          <t>Iago Aspas</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -9179,22 +9179,22 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>53df321ae5c94c6a08000200</t>
+          <t>505d8a247e438909310001c5</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Marcos Llorente</t>
+          <t>Rubén García</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -9206,22 +9206,22 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>521464ea0c36b84d02000024</t>
+          <t>53df321ae5c94c6a08000200</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Raúl de Tomás</t>
+          <t>Marcos Llorente</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -9233,22 +9233,22 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>52017ff55430e20e34000036</t>
+          <t>521464ea0c36b84d02000024</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Foulquier</t>
+          <t>Raúl de Tomás</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -9260,12 +9260,12 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>5218979184abda6d26000258</t>
+          <t>52017ff55430e20e34000036</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Dimitrievski</t>
+          <t>Foulquier</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -9275,7 +9275,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -9287,22 +9287,22 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>50f47dd1dbbab36d0e0042e3</t>
+          <t>5218979184abda6d26000258</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Jonny</t>
+          <t>Dimitrievski</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
@@ -9314,17 +9314,17 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>5255d8008e3e4c1352000369</t>
+          <t>50f47dd1dbbab36d0e0042e3</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Odriozola</t>
+          <t>Jonny</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -9341,22 +9341,22 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>56ff01f1f4bbe2a5799eb126</t>
+          <t>5255d8008e3e4c1352000369</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Kike García</t>
+          <t>Odriozola</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -9368,22 +9368,22 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>54b25febc9360f7e58002e7c</t>
+          <t>56ff01f1f4bbe2a5799eb126</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Berenguer</t>
+          <t>Kike García</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -9395,22 +9395,22 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>504f50d44d8bec9a6700040e</t>
+          <t>54b25febc9360f7e58002e7c</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Ayoze Pérez</t>
+          <t>Berenguer</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
@@ -9422,22 +9422,22 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>55916197c498293442727262</t>
+          <t>504f50d44d8bec9a6700040e</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Unai Simón</t>
+          <t>Ayoze Pérez</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
@@ -9449,22 +9449,22 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>52013ee178b20d7f07000351</t>
+          <t>55916197c498293442727262</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Josan</t>
+          <t>Unai Simón</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -9476,22 +9476,22 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>575c2bacaf91c7b04d8c2513</t>
+          <t>52013ee178b20d7f07000351</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Boyé</t>
+          <t>Josan</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -9503,22 +9503,22 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>535d291c74bf632c030004d2</t>
+          <t>575c2bacaf91c7b04d8c2513</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Gayá</t>
+          <t>Boyé</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
@@ -9530,22 +9530,22 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>504f65184d8bec9a670005f7</t>
+          <t>535d291c74bf632c030004d2</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Isco</t>
+          <t>Gayá</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
@@ -9557,22 +9557,22 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>5659df7ca6379cbb070b8d84</t>
+          <t>504f65184d8bec9a670005f7</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Oyarzabal</t>
+          <t>Isco</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
@@ -9584,22 +9584,22 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>5218a3a884abda6d26000265</t>
+          <t>5659df7ca6379cbb070b8d84</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Álvaro García</t>
+          <t>Oyarzabal</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
@@ -9611,17 +9611,17 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>53a01453b33bed3b010002b1</t>
+          <t>5218a3a884abda6d26000265</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Denis Suárez</t>
+          <t>Álvaro García</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -9638,22 +9638,22 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>504f65024d8bec9a670005aa</t>
+          <t>53a01453b33bed3b010002b1</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Bigas</t>
+          <t>Denis Suárez</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
@@ -9665,22 +9665,22 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>57c09dd1f40c42594caa2956</t>
+          <t>504f65024d8bec9a670005aa</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Marc Roca</t>
+          <t>Bigas</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
@@ -9692,22 +9692,22 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>51c1ca53c7694f5f66000015</t>
+          <t>57c09dd1f40c42594caa2956</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Rüdiger</t>
+          <t>Marc Roca</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
@@ -9719,17 +9719,17 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>51bcc43bb9eca82e1a000011</t>
+          <t>51c1ca53c7694f5f66000015</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Marcos Alonso</t>
+          <t>Rüdiger</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -9746,22 +9746,22 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>51b897a5e401a15f2c000139</t>
+          <t>51bcc43bb9eca82e1a000011</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Gerard Moreno</t>
+          <t>Marcos Alonso</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
@@ -9773,22 +9773,22 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>5606c6f48ec803b3053e1b04</t>
+          <t>51b897a5e401a15f2c000139</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Fornals</t>
+          <t>Gerard Moreno</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -9800,12 +9800,12 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>51aa7cb4a56ca45802050abe</t>
+          <t>5606c6f48ec803b3053e1b04</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Diego Llorente</t>
+          <t>Fornals</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
@@ -9827,22 +9827,22 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>548336cc78a053bf06000ce5</t>
+          <t>51aa7cb4a56ca45802050abe</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Iñaki Williams</t>
+          <t>Diego Llorente</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
@@ -9854,22 +9854,22 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>598b2b3e96ef719d4b46b147</t>
+          <t>548336cc78a053bf06000ce5</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Barja</t>
+          <t>Iñaki Williams</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
@@ -9881,17 +9881,17 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>5962a95af5056e652d290af9</t>
+          <t>598b2b3e96ef719d4b46b147</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Tete Morente</t>
+          <t>Barja</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -9908,22 +9908,22 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>592c5d96e0882ebf0514d517</t>
+          <t>5962a95af5056e652d290af9</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Gabriel Suazo</t>
+          <t>Tete Morente</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
@@ -9935,22 +9935,22 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>57e816de3c438763749abb90</t>
+          <t>592c5d96e0882ebf0514d517</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Álvaro Fernández</t>
+          <t>Gabriel Suazo</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
@@ -9962,22 +9962,22 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>5b33dff53200b74d1d72171e</t>
+          <t>57e816de3c438763749abb90</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Catena</t>
+          <t>Álvaro Fernández</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
@@ -9989,17 +9989,17 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>5b35434b6268503b1d665ec1</t>
+          <t>5b33dff53200b74d1d72171e</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Diakhaby</t>
+          <t>Catena</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -10016,12 +10016,12 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>5a00fee9772e5c4f5827fbeb</t>
+          <t>5b35434b6268503b1d665ec1</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Guido Rodríguez</t>
+          <t>Diakhaby</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -10031,7 +10031,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
@@ -10043,22 +10043,22 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>5d51a911d191dc3feef552c0</t>
+          <t>5a00fee9772e5c4f5827fbeb</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Balliu</t>
+          <t>Guido Rodríguez</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
@@ -10070,22 +10070,22 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>5b89b1161c0c9f16f9678cba</t>
+          <t>5d51a911d191dc3feef552c0</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Lo Celso</t>
+          <t>Balliu</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
@@ -10097,17 +10097,17 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>5d6d88ad1ad6ea0475d2ea30</t>
+          <t>5b89b1161c0c9f16f9678cba</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Ciss</t>
+          <t>Lo Celso</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -10124,17 +10124,17 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>5d01a0892111645ef81548f8</t>
+          <t>5d6d88ad1ad6ea0475d2ea30</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>De Jong</t>
+          <t>Ciss</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -10151,22 +10151,22 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>60b40cb9d2d7f04662cc9c19</t>
+          <t>5d01a0892111645ef81548f8</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Omar</t>
+          <t>De Jong</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
@@ -10178,22 +10178,22 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>5d4bf0557474677ad684915a</t>
+          <t>60b40cb9d2d7f04662cc9c19</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Pedri</t>
+          <t>Omar</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
@@ -10205,22 +10205,22 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>60d6578de348bc03e95ba4b2</t>
+          <t>5d4bf0557474677ad684915a</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Copete</t>
+          <t>Pedri</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
@@ -10232,22 +10232,22 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>612183f216ab17088eaf36b1</t>
+          <t>60d6578de348bc03e95ba4b2</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Satriano</t>
+          <t>Copete</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
@@ -10259,22 +10259,22 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>5d5ea4ec12a917530bc3e4b0</t>
+          <t>612183f216ab17088eaf36b1</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Kubo</t>
+          <t>Satriano</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
@@ -10286,22 +10286,22 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>5d8a75210298d1049e864191</t>
+          <t>5d5ea4ec12a917530bc3e4b0</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Raúl</t>
+          <t>Kubo</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
@@ -10313,22 +10313,22 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>61d98435c40342041fe941b4</t>
+          <t>5d8a75210298d1049e864191</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Leo Román</t>
+          <t>Raúl</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
@@ -10340,22 +10340,22 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>5f45502cae94c503ccbd573f</t>
+          <t>61d98435c40342041fe941b4</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Fidalgo</t>
+          <t>Leo Román</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
@@ -10367,17 +10367,17 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>62d034b9fbbaa82d7199978b</t>
+          <t>5f45502cae94c503ccbd573f</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Beñat Prados</t>
+          <t>Fidalgo</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
@@ -10394,22 +10394,22 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>5f6b104d6a93e44a2fcc725e</t>
+          <t>62d034b9fbbaa82d7199978b</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Cristian Rivero</t>
+          <t>Beñat Prados</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
@@ -10421,22 +10421,22 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>6494b8e92ba0ab1e468b7f35</t>
+          <t>5f6b104d6a93e44a2fcc725e</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Bellingham</t>
+          <t>Cristian Rivero</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
@@ -10448,17 +10448,17 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>64c039a313c6a63ccc321929</t>
+          <t>6494b8e92ba0ab1e468b7f35</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Luismi Cruz</t>
+          <t>Bellingham</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
@@ -10475,22 +10475,22 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>5fecc9d86ede9207a9f2fcac</t>
+          <t>64c039a313c6a63ccc321929</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Juan Iglesias</t>
+          <t>Luismi Cruz</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
@@ -10502,22 +10502,22 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>64e53d084068dc518b94a054</t>
+          <t>5fecc9d86ede9207a9f2fcac</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Zakharyan</t>
+          <t>Juan Iglesias</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
@@ -10529,17 +10529,17 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>6080ace3876c8206f41c4197</t>
+          <t>64e53d084068dc518b94a054</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Blanco</t>
+          <t>Zakharyan</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
@@ -10556,22 +10556,22 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>66802f240c14414136e408c3</t>
+          <t>6080ace3876c8206f41c4197</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Mella</t>
+          <t>Blanco</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
@@ -10583,22 +10583,22 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>6110e7e0c16ee36065aa49bd</t>
+          <t>66802f240c14414136e408c3</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Agirrezabala</t>
+          <t>Mella</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
@@ -10610,17 +10610,17 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>6685186cd766964157307273</t>
+          <t>6110e7e0c16ee36065aa49bd</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Vlachodimos</t>
+          <t>Agirrezabala</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
@@ -10637,22 +10637,22 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>62a67388de8e9e03e103990b</t>
+          <t>6685186cd766964157307273</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Tchouameni</t>
+          <t>Vlachodimos</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
@@ -10664,22 +10664,22 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>6692e7f199e2e504052cb421</t>
+          <t>62a67388de8e9e03e103990b</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Letacek</t>
+          <t>Tchouameni</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
@@ -10691,22 +10691,22 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>62c81fc9deea5c2d8c81fe13</t>
+          <t>6692e7f199e2e504052cb421</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Peque</t>
+          <t>Letacek</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
@@ -10718,22 +10718,22 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>6861a4f450c8fc331b6365a2</t>
+          <t>62c81fc9deea5c2d8c81fe13</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Gerenabarrena</t>
+          <t>Peque</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
@@ -10745,22 +10745,22 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>64b8620a5595c73cc509b299</t>
+          <t>6861a4f450c8fc331b6365a2</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Alemão</t>
+          <t>Gerenabarrena</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
@@ -10772,22 +10772,22 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>68a3a86d3a1cb503e4687030</t>
+          <t>64b8620a5595c73cc509b299</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Martim Neto</t>
+          <t>Alemão</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
@@ -10799,22 +10799,22 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>64d156d341f8d73d235026fb</t>
+          <t>68a3a86d3a1cb503e4687030</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Natan</t>
+          <t>Martim Neto</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
@@ -10826,22 +10826,22 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>6961830c619f3203bc795c50</t>
+          <t>64d156d341f8d73d235026fb</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Joselu</t>
+          <t>Natan</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
@@ -10853,22 +10853,22 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>64e53d94a577ee5151c0b1f4</t>
+          <t>6961830c619f3203bc795c50</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Unai Marrero</t>
+          <t>Joselu</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
@@ -10880,22 +10880,22 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>6599dd40a4082870148ee34a</t>
+          <t>64e53d94a577ee5151c0b1f4</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Huijsen</t>
+          <t>Unai Marrero</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
@@ -10907,17 +10907,17 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>65aac8411342fe045bb822e2</t>
+          <t>6599dd40a4082870148ee34a</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Tárrega</t>
+          <t>Huijsen</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
@@ -10934,17 +10934,17 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>6a4d1bfcae633549bd0f0744</t>
+          <t>65aac8411342fe045bb822e2</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Bright Ede</t>
+          <t>Tárrega</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
@@ -10961,22 +10961,22 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>6653899c36df000455d63bf7</t>
+          <t>6a4d1bfcae633549bd0f0744</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Espí</t>
+          <t>Bright Ede</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
@@ -10988,22 +10988,22 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>66b78ac399e2e504052cbe93</t>
+          <t>6653899c36df000455d63bf7</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Marc Bernal</t>
+          <t>Espí</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
@@ -11015,22 +11015,22 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>66cfa0f08be9a7041ad309f9</t>
+          <t>66b78ac399e2e504052cbe93</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Jon Martín</t>
+          <t>Marc Bernal</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
@@ -11042,22 +11042,22 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>6823c91b81f9dd0429e625ac</t>
+          <t>66cfa0f08be9a7041ad309f9</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Redondo</t>
+          <t>Jon Martín</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
@@ -11069,22 +11069,22 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>68a1066311d65103ec0070ef</t>
+          <t>6823c91b81f9dd0429e625ac</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>El-Abdellaoui</t>
+          <t>Redondo</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
@@ -11096,22 +11096,22 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>69b6fc4a1c66b403a1223d3d</t>
+          <t>68a1066311d65103ec0070ef</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Espart</t>
+          <t>El-Abdellaoui</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
@@ -11123,17 +11123,17 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>6a43e860e284b949d26e1c3c</t>
+          <t>69b6fc4a1c66b403a1223d3d</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grimaldo </t>
+          <t>Espart</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
@@ -11150,22 +11150,22 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>6a621c32c6d839058e965748</t>
+          <t>6a43e860e284b949d26e1c3c</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Adeyemi</t>
+          <t xml:space="preserve">Grimaldo </t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
@@ -11177,22 +11177,22 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>58cd754bafa5feac0520edda</t>
+          <t>6a621c32c6d839058e965748</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Guridi</t>
+          <t>Adeyemi</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
@@ -11204,22 +11204,22 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>59c7ab546c064c993bc73462</t>
+          <t>58cd754bafa5feac0520edda</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Luiz Felipe</t>
+          <t>Guridi</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
@@ -11231,22 +11231,22 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>594ad95d4ba3892d2226454c</t>
+          <t>59c7ab546c064c993bc73462</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Bernardo Silva</t>
+          <t>Luiz Felipe</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
@@ -11258,17 +11258,17 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>5cb344adaa68df0442669528</t>
+          <t>594ad95d4ba3892d2226454c</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Barrenetxea</t>
+          <t>Bernardo Silva</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
@@ -11285,12 +11285,12 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>59a9a9027d26b96314916033</t>
+          <t>5cb344adaa68df0442669528</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Guedes</t>
+          <t>Barrenetxea</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
@@ -11312,22 +11312,22 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>5e2b73e8a7992b52c0641b93</t>
+          <t>59a9a9027d26b96314916033</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Manu Hernando</t>
+          <t>Guedes</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
@@ -11339,22 +11339,22 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>5b7864b259b3992b14aa4bc0</t>
+          <t>5e2b73e8a7992b52c0641b93</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Puado</t>
+          <t>Manu Hernando</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
@@ -11366,22 +11366,22 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>5f14b970f8e4ae03c1f96475</t>
+          <t>5b7864b259b3992b14aa4bc0</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Aimar Oroz</t>
+          <t>Puado</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
@@ -11393,22 +11393,22 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>5f75f6ff5efb030404be8b77</t>
+          <t>5f14b970f8e4ae03c1f96475</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Lookman</t>
+          <t>Aimar Oroz</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
@@ -11420,22 +11420,22 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>5f78e79033215d0412a634a7</t>
+          <t>5f75f6ff5efb030404be8b77</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Larrubia</t>
+          <t>Lookman</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
@@ -11447,17 +11447,17 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>601869861554ce07d665766f</t>
+          <t>5f78e79033215d0412a634a7</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Germán Valera</t>
+          <t>Larrubia</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
@@ -11474,22 +11474,22 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>60ed485214bb466048d3a5db</t>
+          <t>601869861554ce07d665766f</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Areso</t>
+          <t>Germán Valera</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
@@ -11501,17 +11501,17 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>607b5df9e292620d106cbb8e</t>
+          <t>60ed485214bb466048d3a5db</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Chust</t>
+          <t>Areso</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
@@ -11528,22 +11528,22 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>610ab7f51a405a604ca8c374</t>
+          <t>607b5df9e292620d106cbb8e</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Moleiro</t>
+          <t>Chust</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
@@ -11555,17 +11555,17 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>611e6d65c6657008542a1453</t>
+          <t>610ab7f51a405a604ca8c374</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Raúl Moro</t>
+          <t>Moleiro</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
@@ -11582,17 +11582,17 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>61996290d61a5d094f43a4bd</t>
+          <t>611e6d65c6657008542a1453</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Ilias Akhomach</t>
+          <t>Raúl Moro</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
@@ -11609,22 +11609,22 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>61c0eb88278f443e1e5d6a71</t>
+          <t>61996290d61a5d094f43a4bd</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Pubill</t>
+          <t>Ilias Akhomach</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
@@ -11636,17 +11636,17 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>62b31101deea5c2d8c81fdf5</t>
+          <t>61c0eb88278f443e1e5d6a71</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Dela</t>
+          <t>Pubill</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
@@ -11663,17 +11663,17 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>62e0f3d5fbbaa82d719997a2</t>
+          <t>62b31101deea5c2d8c81fdf5</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Quagliata</t>
+          <t>Dela</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
@@ -11690,17 +11690,17 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>62e58d3e11f4242dbd72531a</t>
+          <t>62e0f3d5fbbaa82d719997a2</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>José Salinas</t>
+          <t>Quagliata</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
@@ -11717,22 +11717,22 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>62ee482f2f093467dc60108e</t>
+          <t>62e58d3e11f4242dbd72531a</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Pablo Ibáñez</t>
+          <t>José Salinas</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
@@ -11744,17 +11744,17 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>630d3c68b640225ddc5861c9</t>
+          <t>62ee482f2f093467dc60108e</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Fran Pérez</t>
+          <t>Pablo Ibáñez</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
@@ -11771,17 +11771,17 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>635d5731fab08a089c78801c</t>
+          <t>630d3c68b640225ddc5861c9</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Pablo Barrios</t>
+          <t>Fran Pérez</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
@@ -11798,22 +11798,22 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>64d2b9156167273d0ccc5c4f</t>
+          <t>635d5731fab08a089c78801c</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Facundo González</t>
+          <t>Pablo Barrios</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
@@ -11825,22 +11825,22 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>6595c864840719702ac42c2a</t>
+          <t>64d2b9156167273d0ccc5c4f</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Hugo Álvarez</t>
+          <t>Facundo González</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
@@ -11852,22 +11852,22 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>65ac4fa5fa23880455a78f95</t>
+          <t>6595c864840719702ac42c2a</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Aramburu</t>
+          <t>Hugo Álvarez</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
@@ -11879,22 +11879,22 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>65988cd903b798703d8cc061</t>
+          <t>65ac4fa5fa23880455a78f95</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Buchanan</t>
+          <t>Aramburu</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
@@ -11906,22 +11906,22 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>65db9c727da3ff03e6654f00</t>
+          <t>65988cd903b798703d8cc061</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Arguibide</t>
+          <t>Buchanan</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
@@ -11933,22 +11933,22 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>65a14cffd9c62803f70f8509</t>
+          <t>65db9c727da3ff03e6654f00</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Isaac Romero</t>
+          <t>Arguibide</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
@@ -11960,22 +11960,22 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>6623fd0e5d937903d96ecca1</t>
+          <t>65a14cffd9c62803f70f8509</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Cabello</t>
+          <t>Isaac Romero</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
@@ -11987,22 +11987,22 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>66453408943e1536068fa651</t>
+          <t>6623fd0e5d937903d96ecca1</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Risco</t>
+          <t>Cabello</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
@@ -12014,22 +12014,22 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>66a3cafd9e452303b3fc0b5e</t>
+          <t>66453408943e1536068fa651</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>A. Osorio</t>
+          <t>Risco</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
@@ -12041,22 +12041,22 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>665ced2c03b5e9046aff4b19</t>
+          <t>66a3cafd9e452303b3fc0b5e</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Bauza</t>
+          <t>A. Osorio</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
@@ -12068,17 +12068,17 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>66b6a02fe0157a03f87fcb94</t>
+          <t>665ced2c03b5e9046aff4b19</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Gorrotxategi</t>
+          <t>Bauza</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
@@ -12095,17 +12095,17 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>666b0e4336df000455d656d4</t>
+          <t>66b6a02fe0157a03f87fcb94</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Christantus Uche</t>
+          <t>Gorrotxategi</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
@@ -12122,22 +12122,22 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>66802cdbfd03ab41756b1dc9</t>
+          <t>666b0e4336df000455d656d4</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Dani Barcia</t>
+          <t>Christantus Uche</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
@@ -12149,17 +12149,17 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>66d0a0d48be9a7041ad30d08</t>
+          <t>66802cdbfd03ab41756b1dc9</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Egiluz</t>
+          <t>Dani Barcia</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
@@ -12176,22 +12176,22 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>6780ea6d98d6a37581d90469</t>
+          <t>66d0a0d48be9a7041ad30d08</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Vargas</t>
+          <t>Egiluz</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
@@ -12203,22 +12203,22 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>66a9874cce303803d6f77525</t>
+          <t>6780ea6d98d6a37581d90469</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Yago Santiago</t>
+          <t>Vargas</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
@@ -12230,22 +12230,22 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>682893686f9b99317afd9034</t>
+          <t>66a9874cce303803d6f77525</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>F. Cardoso</t>
+          <t>Yago Santiago</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
@@ -12257,22 +12257,22 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>66c5102b8be9a7041ad2df88</t>
+          <t>682893686f9b99317afd9034</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Luiz Junior</t>
+          <t>F. Cardoso</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
@@ -12284,22 +12284,22 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>6865a9767775a433449e9c85</t>
+          <t>66c5102b8be9a7041ad2df88</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Noubi</t>
+          <t>Luiz Junior</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
@@ -12311,22 +12311,22 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>66d2486c099be403f1da8033</t>
+          <t>6865a9767775a433449e9c85</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Óskarsson</t>
+          <t>Noubi</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
@@ -12338,22 +12338,22 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>6884c2ae19c279041887fa84</t>
+          <t>66d2486c099be403f1da8033</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Valentín Gómez</t>
+          <t>Óskarsson</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
@@ -12365,22 +12365,22 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>679d3d34fdee6403d89449fe</t>
+          <t>6884c2ae19c279041887fa84</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Eddahchouri</t>
+          <t>Valentín Gómez</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
@@ -12392,22 +12392,22 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>68ebfeadaff4d55004ae1572</t>
+          <t>679d3d34fdee6403d89449fe</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Rafita</t>
+          <t>Eddahchouri</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
@@ -12419,22 +12419,22 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>67eeb84cb5d12f043f14e638</t>
+          <t>68ebfeadaff4d55004ae1572</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Fran González</t>
+          <t>Rafita</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
@@ -12446,22 +12446,22 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>68c735dbd4204b55b4125678</t>
+          <t>67eeb84cb5d12f043f14e638</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Roony</t>
+          <t>Fran González</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
@@ -12473,22 +12473,22 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>697bdf4c8d994403fc68fa11</t>
+          <t>68c735dbd4204b55b4125678</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Freeman</t>
+          <t>Roony</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
@@ -12500,22 +12500,22 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>6a4d1b4e2ae0d649eac3a152</t>
+          <t>697bdf4c8d994403fc68fa11</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Bernal</t>
+          <t>Freeman</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
@@ -12527,17 +12527,17 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>594d11088a928dbb0555e5a6</t>
+          <t>6a4d1b4e2ae0d649eac3a152</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Fede Valverde</t>
+          <t>Bernal</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
@@ -12554,17 +12554,17 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>5a2d6f2fd168259b3ede4aef</t>
+          <t>594d11088a928dbb0555e5a6</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Aitor Ruibal</t>
+          <t>Fede Valverde</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
@@ -12581,22 +12581,22 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>5c03bd490f4a903b890cd3da</t>
+          <t>5a2d6f2fd168259b3ede4aef</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Le Normand</t>
+          <t>Aitor Ruibal</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
@@ -12608,17 +12608,17 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>5989a4391f9fb9af4ba1b806</t>
+          <t>5c03bd490f4a903b890cd3da</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Calero</t>
+          <t>Le Normand</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
@@ -12635,17 +12635,17 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>5f8b0f52406daa4fc599cfa0</t>
+          <t>5989a4391f9fb9af4ba1b806</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Carreira</t>
+          <t>Calero</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
@@ -12662,17 +12662,17 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>60b416c715f5654650f8e413</t>
+          <t>5f8b0f52406daa4fc599cfa0</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Sergi Cardona</t>
+          <t>Carreira</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
@@ -12689,22 +12689,22 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>5a23f0b68a9f96c2332504ab</t>
+          <t>60b416c715f5654650f8e413</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Raba</t>
+          <t>Sergi Cardona</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
@@ -12716,22 +12716,22 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>60dec77388c3b1602f5b3ae6</t>
+          <t>5a23f0b68a9f96c2332504ab</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Konaté</t>
+          <t>Raba</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
@@ -12743,22 +12743,22 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>5ac29d32c8bf976d1c180107</t>
+          <t>60dec77388c3b1602f5b3ae6</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Hugo Duro</t>
+          <t>Konaté</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
@@ -12770,17 +12770,17 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>61122ac42806395bcad477f0</t>
+          <t>5ac29d32c8bf976d1c180107</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Brugué</t>
+          <t>Hugo Duro</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
@@ -12797,22 +12797,22 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>5d0220e0167d9e5eb611db94</t>
+          <t>61122ac42806395bcad477f0</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Pol Lozano</t>
+          <t>Brugué</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
@@ -12824,17 +12824,17 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>612e5dd7c44d9506f10f8fed</t>
+          <t>5d0220e0167d9e5eb611db94</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>Camavinga</t>
+          <t>Pol Lozano</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
@@ -12851,22 +12851,22 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>5d430c1e2099e47b0f3d7650</t>
+          <t>612e5dd7c44d9506f10f8fed</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Danjuma</t>
+          <t>Camavinga</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E461" t="inlineStr">
@@ -12878,12 +12878,12 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>614f52757bf8f60892e55d4a</t>
+          <t>5d430c1e2099e47b0f3d7650</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Jesús Vázquez</t>
+          <t>Danjuma</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -12893,7 +12893,7 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
@@ -12905,22 +12905,22 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>61b51da6d1dcc206d030bacc</t>
+          <t>614f52757bf8f60892e55d4a</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Dani Lorenzo</t>
+          <t>Jesús Vázquez</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E463" t="inlineStr">
@@ -12932,22 +12932,22 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>6089b8ace0c69806f612a3d4</t>
+          <t>61b51da6d1dcc206d030bacc</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Nico Williams</t>
+          <t>Dani Lorenzo</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
@@ -12959,22 +12959,22 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>62b30b7011f4242dbd7252b0</t>
+          <t>6089b8ace0c69806f612a3d4</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>Mantilla</t>
+          <t>Nico Williams</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
@@ -12986,22 +12986,22 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>610174c4bc32266071ced17a</t>
+          <t>62b30b7011f4242dbd7252b0</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Oriol Rey</t>
+          <t>Mantilla</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
@@ -13013,22 +13013,22 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>62f826f93355b0168987308d</t>
+          <t>610174c4bc32266071ced17a</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>Abqar</t>
+          <t>Oriol Rey</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E467" t="inlineStr">
@@ -13040,22 +13040,22 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>61122a78c7c51f5b9a6ca7c4</t>
+          <t>62f826f93355b0168987308d</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>Pepelu</t>
+          <t>Abqar</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E468" t="inlineStr">
@@ -13067,12 +13067,12 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>630d3bceb4ad355e01bea95f</t>
+          <t>61122a78c7c51f5b9a6ca7c4</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>Diego López</t>
+          <t>Pepelu</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -13082,7 +13082,7 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
@@ -13094,22 +13094,22 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>61184f3ad8a84f5bb9a7fe9d</t>
+          <t>630d3bceb4ad355e01bea95f</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>Dumfries</t>
+          <t>Diego López</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
@@ -13121,17 +13121,17 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>63375e14c376ff465d2a5af7</t>
+          <t>61184f3ad8a84f5bb9a7fe9d</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Aitor Paredes</t>
+          <t>Dumfries</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
@@ -13148,17 +13148,17 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>614204ec48f6a015444ac7df</t>
+          <t>63375e14c376ff465d2a5af7</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Balde</t>
+          <t>Aitor Paredes</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
@@ -13175,17 +13175,17 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>64516ff73917190401517dfb</t>
+          <t>614204ec48f6a015444ac7df</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Herrando</t>
+          <t>Balde</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
@@ -13202,22 +13202,22 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>62adceb2b2a1132d77c95779</t>
+          <t>64516ff73917190401517dfb</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Swedberg</t>
+          <t>Herrando</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
@@ -13229,22 +13229,22 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>64a6fcb014cd337373737ba9</t>
+          <t>62adceb2b2a1132d77c95779</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Güler</t>
+          <t>Swedberg</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
@@ -13256,17 +13256,17 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>62ae4ce2c057ca2d85a004e2</t>
+          <t>64a6fcb014cd337373737ba9</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Hjulmand</t>
+          <t>Güler</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
@@ -13283,22 +13283,22 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>655be3da0cc5192b1a75785c</t>
+          <t>62ae4ce2c057ca2d85a004e2</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Xavi Grande</t>
+          <t>Hjulmand</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
@@ -22023,6 +22023,33 @@
         </is>
       </c>
       <c r="E800" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>6aaaea51544fa503d314ea2d</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>Unai Santos</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>504e581e4d8bec9a670000d1</t>
+        </is>
+      </c>
+      <c r="D801" t="inlineStr">
+        <is>
+          <t>defensa</t>
+        </is>
+      </c>
+      <c r="E801" t="inlineStr">
         <is>
           <t>2025/26</t>
         </is>

--- a/datos/maestros/md_jugadores.xlsx
+++ b/datos/maestros/md_jugadores.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E801"/>
+  <dimension ref="A1:E802"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22055,6 +22055,33 @@
         </is>
       </c>
     </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>6aadafc332f5fd03be220793</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>José Ángel</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>504e581e4d8bec9a670000d0</t>
+        </is>
+      </c>
+      <c r="D802" t="inlineStr">
+        <is>
+          <t>defensa</t>
+        </is>
+      </c>
+      <c r="E802" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
